--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 알파 전투 밸런스 데이터 테이블 V2.0.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 알파 전투 밸런스 데이터 테이블 V2.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\개인\게임인재원 7기\Hero Influence\기획서\Hero Influence_강현재\밸런스\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HeroInfluencetmp\Assets\_ProtoType_Merge\ASB\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48657B2B-D16A-4F8D-8443-7789CEE3246C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDC38A7-4E31-48C2-A568-A43977B431A8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="834" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="834" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수정 내역" sheetId="41" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="549">
   <si>
     <t>Class</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -2304,13 +2304,17 @@
     <t>{HC001,HC002,HC003,HC004,HC005}</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>list&lt;string&gt;</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="mm\/dd"/>
+    <numFmt numFmtId="176" formatCode="mm\/dd"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -2569,18 +2573,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="5" applyFont="1">
@@ -2628,7 +2620,19 @@
     <xf numFmtId="3" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3285,10 +3289,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC70340-B386-46F7-B380-7E3B46561623}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="122.875" customWidth="1"/>
+    <col min="3" max="3" width="122.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -3297,18 +3301,18 @@
       </c>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="49">
+      <c r="B3" s="45">
         <v>46196</v>
       </c>
       <c r="C3" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="320.64999999999998">
-      <c r="B4" s="49">
+    <row r="4" spans="2:3" ht="323">
+      <c r="B4" s="45">
         <v>46209</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="29" t="s">
         <v>489</v>
       </c>
     </row>
@@ -3322,18 +3326,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0AF93A4-1273-423C-B589-7C2465F14193}">
   <dimension ref="A1:Q22"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="10.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="15.5625" style="11" customWidth="1"/>
-    <col min="5" max="5" width="33.4375" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="12" width="15.5625" style="11" customWidth="1"/>
+    <col min="2" max="4" width="15.58203125" style="11" customWidth="1"/>
+    <col min="5" max="5" width="33.4140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="12" width="15.58203125" style="11" customWidth="1"/>
     <col min="13" max="13" width="37.75" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="32" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="25" style="11" customWidth="1"/>
-    <col min="16" max="16" width="24.5625" style="11" customWidth="1"/>
-    <col min="17" max="17" width="24.3125" style="11" customWidth="1"/>
-    <col min="18" max="62" width="15.5625" style="11" customWidth="1"/>
+    <col min="16" max="16" width="24.58203125" style="11" customWidth="1"/>
+    <col min="17" max="17" width="24.33203125" style="11" customWidth="1"/>
+    <col min="18" max="62" width="15.58203125" style="11" customWidth="1"/>
     <col min="63" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
@@ -3343,30 +3347,30 @@
       </c>
     </row>
     <row r="2" spans="1:17">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="46" t="s">
         <v>217</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="7" t="s">
         <v>182</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>19</v>
@@ -3399,10 +3403,10 @@
         <v>18</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>22</v>
+        <v>548</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>22</v>
+        <v>548</v>
       </c>
       <c r="O4" s="7" t="s">
         <v>18</v>
@@ -3467,7 +3471,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="33.75">
+    <row r="6" spans="1:17" ht="34">
       <c r="A6" s="7" t="s">
         <v>185</v>
       </c>
@@ -3501,13 +3505,13 @@
       <c r="K6" s="16">
         <v>0.15</v>
       </c>
-      <c r="L6" s="38">
-        <v>1</v>
-      </c>
-      <c r="M6" s="48" t="s">
+      <c r="L6" s="34">
+        <v>1</v>
+      </c>
+      <c r="M6" s="44" t="s">
         <v>543</v>
       </c>
-      <c r="N6" s="38" t="s">
+      <c r="N6" s="34" t="s">
         <v>547</v>
       </c>
       <c r="O6" s="17">
@@ -3520,7 +3524,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="33.75">
+    <row r="7" spans="1:17" ht="34">
       <c r="A7" s="7"/>
       <c r="B7" s="8">
         <v>10002</v>
@@ -3555,10 +3559,10 @@
       <c r="L7" s="8">
         <v>3</v>
       </c>
-      <c r="M7" s="48" t="s">
+      <c r="M7" s="44" t="s">
         <v>544</v>
       </c>
-      <c r="N7" s="38" t="s">
+      <c r="N7" s="34" t="s">
         <v>547</v>
       </c>
       <c r="O7" s="17">
@@ -3571,7 +3575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="33.75">
+    <row r="8" spans="1:17" ht="34">
       <c r="A8" s="7"/>
       <c r="B8" s="8">
         <v>10003</v>
@@ -3606,10 +3610,10 @@
       <c r="L8" s="8">
         <v>2</v>
       </c>
-      <c r="M8" s="48" t="s">
+      <c r="M8" s="44" t="s">
         <v>545</v>
       </c>
-      <c r="N8" s="38" t="s">
+      <c r="N8" s="34" t="s">
         <v>547</v>
       </c>
       <c r="O8" s="17">
@@ -3622,7 +3626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="33.75">
+    <row r="9" spans="1:17" ht="34">
       <c r="A9" s="7"/>
       <c r="B9" s="8">
         <v>10004</v>
@@ -3657,10 +3661,10 @@
       <c r="L9" s="8">
         <v>2</v>
       </c>
-      <c r="M9" s="48" t="s">
+      <c r="M9" s="44" t="s">
         <v>546</v>
       </c>
-      <c r="N9" s="38" t="s">
+      <c r="N9" s="34" t="s">
         <v>547</v>
       </c>
       <c r="O9" s="17">
@@ -3708,7 +3712,7 @@
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:17" ht="33.75">
+    <row r="12" spans="1:17" ht="34">
       <c r="A12" s="11" t="s">
         <v>181</v>
       </c>
@@ -3924,23 +3928,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB586D60-C112-4BDA-9620-A63D44BCE4B4}">
   <dimension ref="A1:N32"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="10.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="15.5625" style="11" customWidth="1"/>
-    <col min="4" max="4" width="24.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.58203125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="24.08203125" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.3125" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5625" style="11" customWidth="1"/>
+    <col min="6" max="6" width="18.08203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.08203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.58203125" style="11" customWidth="1"/>
     <col min="11" max="11" width="37.75" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="56.9375" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="56.9140625" style="11" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="25" style="11" customWidth="1"/>
-    <col min="14" max="14" width="24.5625" style="11" customWidth="1"/>
-    <col min="15" max="15" width="24.3125" style="11" customWidth="1"/>
-    <col min="16" max="60" width="15.5625" style="11" customWidth="1"/>
+    <col min="14" max="14" width="24.58203125" style="11" customWidth="1"/>
+    <col min="15" max="15" width="24.33203125" style="11" customWidth="1"/>
+    <col min="16" max="60" width="15.58203125" style="11" customWidth="1"/>
     <col min="61" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
@@ -3950,21 +3954,21 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="48" t="s">
         <v>217</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="11" t="s">
@@ -3982,17 +3986,17 @@
       <c r="E4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="20" t="s">
-        <v>18</v>
+      <c r="F4" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="30" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -4011,16 +4015,16 @@
       <c r="E5" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="F5" s="36" t="s">
+      <c r="F5" s="32" t="s">
         <v>537</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="G5" s="32" t="s">
         <v>538</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="H5" s="32" t="s">
         <v>535</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="32" t="s">
         <v>536</v>
       </c>
     </row>
@@ -4037,16 +4041,16 @@
       <c r="D6" s="11">
         <v>0</v>
       </c>
-      <c r="F6" s="39" t="s">
+      <c r="F6" s="35" t="s">
         <v>330</v>
       </c>
-      <c r="G6" s="39" t="s">
+      <c r="G6" s="35" t="s">
         <v>395</v>
       </c>
-      <c r="H6" s="39" t="s">
+      <c r="H6" s="35" t="s">
         <v>426</v>
       </c>
-      <c r="I6" s="39" t="s">
+      <c r="I6" s="35" t="s">
         <v>456</v>
       </c>
     </row>
@@ -4063,16 +4067,16 @@
       <c r="E7" s="11">
         <v>10</v>
       </c>
-      <c r="F7" s="39" t="s">
+      <c r="F7" s="35" t="s">
         <v>332</v>
       </c>
-      <c r="G7" s="39" t="s">
+      <c r="G7" s="35" t="s">
         <v>397</v>
       </c>
-      <c r="H7" s="39" t="s">
+      <c r="H7" s="35" t="s">
         <v>428</v>
       </c>
-      <c r="I7" s="39" t="s">
+      <c r="I7" s="35" t="s">
         <v>458</v>
       </c>
     </row>
@@ -4089,16 +4093,16 @@
       <c r="E8" s="11">
         <v>10</v>
       </c>
-      <c r="F8" s="39" t="s">
+      <c r="F8" s="35" t="s">
         <v>334</v>
       </c>
-      <c r="G8" s="39" t="s">
+      <c r="G8" s="35" t="s">
         <v>399</v>
       </c>
-      <c r="H8" s="39" t="s">
+      <c r="H8" s="35" t="s">
         <v>430</v>
       </c>
-      <c r="I8" s="39" t="s">
+      <c r="I8" s="35" t="s">
         <v>460</v>
       </c>
     </row>
@@ -4115,16 +4119,16 @@
       <c r="E9" s="11">
         <v>10</v>
       </c>
-      <c r="F9" s="39" t="s">
+      <c r="F9" s="35" t="s">
         <v>335</v>
       </c>
-      <c r="G9" s="39" t="s">
+      <c r="G9" s="35" t="s">
         <v>401</v>
       </c>
-      <c r="H9" s="39" t="s">
+      <c r="H9" s="35" t="s">
         <v>432</v>
       </c>
-      <c r="I9" s="39" t="s">
+      <c r="I9" s="35" t="s">
         <v>462</v>
       </c>
     </row>
@@ -4141,16 +4145,16 @@
       <c r="E10" s="11">
         <v>10</v>
       </c>
-      <c r="F10" s="39" t="s">
+      <c r="F10" s="35" t="s">
         <v>336</v>
       </c>
-      <c r="G10" s="39" t="s">
+      <c r="G10" s="35" t="s">
         <v>403</v>
       </c>
-      <c r="H10" s="39" t="s">
+      <c r="H10" s="35" t="s">
         <v>434</v>
       </c>
-      <c r="I10" s="39" t="s">
+      <c r="I10" s="35" t="s">
         <v>464</v>
       </c>
     </row>
@@ -4167,16 +4171,16 @@
       <c r="E11" s="11">
         <v>10</v>
       </c>
-      <c r="F11" s="39" t="s">
+      <c r="F11" s="35" t="s">
         <v>338</v>
       </c>
-      <c r="G11" s="39" t="s">
+      <c r="G11" s="35" t="s">
         <v>405</v>
       </c>
-      <c r="H11" s="39" t="s">
+      <c r="H11" s="35" t="s">
         <v>436</v>
       </c>
-      <c r="I11" s="39" t="s">
+      <c r="I11" s="35" t="s">
         <v>466</v>
       </c>
     </row>
@@ -4193,16 +4197,16 @@
       <c r="E12" s="11">
         <v>10</v>
       </c>
-      <c r="F12" s="39" t="s">
+      <c r="F12" s="35" t="s">
         <v>340</v>
       </c>
-      <c r="G12" s="39" t="s">
+      <c r="G12" s="35" t="s">
         <v>407</v>
       </c>
-      <c r="H12" s="39" t="s">
+      <c r="H12" s="35" t="s">
         <v>438</v>
       </c>
-      <c r="I12" s="39" t="s">
+      <c r="I12" s="35" t="s">
         <v>468</v>
       </c>
     </row>
@@ -4219,16 +4223,16 @@
       <c r="E13" s="11">
         <v>20</v>
       </c>
-      <c r="F13" s="39" t="s">
+      <c r="F13" s="35" t="s">
         <v>342</v>
       </c>
-      <c r="G13" s="39" t="s">
+      <c r="G13" s="35" t="s">
         <v>409</v>
       </c>
-      <c r="H13" s="39" t="s">
+      <c r="H13" s="35" t="s">
         <v>440</v>
       </c>
-      <c r="I13" s="39" t="s">
+      <c r="I13" s="35" t="s">
         <v>470</v>
       </c>
     </row>
@@ -4237,7 +4241,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="33.75">
+    <row r="16" spans="1:14" ht="34">
       <c r="A16" s="11" t="s">
         <v>181</v>
       </c>
@@ -4253,16 +4257,16 @@
       <c r="E16" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F16" s="33" t="s">
+      <c r="F16" s="29" t="s">
         <v>539</v>
       </c>
-      <c r="G16" s="33" t="s">
+      <c r="G16" s="29" t="s">
         <v>540</v>
       </c>
-      <c r="H16" s="33" t="s">
+      <c r="H16" s="29" t="s">
         <v>541</v>
       </c>
-      <c r="I16" s="33" t="s">
+      <c r="I16" s="29" t="s">
         <v>542</v>
       </c>
     </row>
@@ -4328,32 +4332,32 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14B0CA0E-333E-418B-A423-137F80889975}">
   <dimension ref="A1:AM29"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="10.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="15.5625" style="11" customWidth="1"/>
-    <col min="4" max="4" width="25.4375" style="11" customWidth="1"/>
-    <col min="5" max="5" width="14.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="12" width="15.5625" style="11" customWidth="1"/>
+    <col min="2" max="3" width="15.58203125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="25.4140625" style="11" customWidth="1"/>
+    <col min="5" max="5" width="14.08203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="12" width="15.58203125" style="11" customWidth="1"/>
     <col min="13" max="13" width="50.75" style="11" customWidth="1"/>
-    <col min="14" max="14" width="36.3125" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="36.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="25" style="11" customWidth="1"/>
-    <col min="16" max="16" width="24.5625" style="11" customWidth="1"/>
-    <col min="17" max="17" width="36.3125" style="11" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="39.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.58203125" style="11" customWidth="1"/>
+    <col min="17" max="17" width="36.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="39.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="61.75" style="11" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="46.0625" style="11" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.5625" style="11" customWidth="1"/>
-    <col min="22" max="22" width="19.1875" style="28" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.5625" style="11" customWidth="1"/>
-    <col min="24" max="24" width="41.5625" style="11" customWidth="1"/>
-    <col min="25" max="32" width="15.5625" style="11" customWidth="1"/>
-    <col min="33" max="33" width="19.1875" style="28" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="46.08203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.58203125" style="11" customWidth="1"/>
+    <col min="22" max="22" width="19.1640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.58203125" style="11" customWidth="1"/>
+    <col min="24" max="24" width="41.58203125" style="11" customWidth="1"/>
+    <col min="25" max="32" width="15.58203125" style="11" customWidth="1"/>
+    <col min="33" max="33" width="19.1640625" style="28" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="70.25" style="11" customWidth="1"/>
-    <col min="35" max="35" width="15.5625" style="11" customWidth="1"/>
-    <col min="36" max="36" width="25.1875" style="28" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="17.5625" style="11" bestFit="1" customWidth="1"/>
-    <col min="38" max="65" width="15.5625" style="11" customWidth="1"/>
+    <col min="35" max="35" width="15.58203125" style="11" customWidth="1"/>
+    <col min="36" max="36" width="25.1640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="17.58203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="38" max="65" width="15.58203125" style="11" customWidth="1"/>
     <col min="66" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
@@ -4363,30 +4367,30 @@
       </c>
     </row>
     <row r="2" spans="1:39">
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="48" t="s">
         <v>221</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
     </row>
     <row r="4" spans="1:39">
       <c r="A4" s="11" t="s">
         <v>182</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>19</v>
@@ -4487,16 +4491,16 @@
       <c r="AI4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="AJ4" s="38" t="s">
+      <c r="AJ4" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="AK4" s="38" t="s">
+      <c r="AK4" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="AL4" s="38" t="s">
+      <c r="AL4" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="AM4" s="38" t="s">
+      <c r="AM4" s="34" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4606,30 +4610,30 @@
       <c r="AI5" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="AJ5" s="39" t="s">
+      <c r="AJ5" s="35" t="s">
         <v>506</v>
       </c>
-      <c r="AK5" s="39" t="s">
+      <c r="AK5" s="35" t="s">
         <v>507</v>
       </c>
-      <c r="AL5" s="39" t="s">
+      <c r="AL5" s="35" t="s">
         <v>508</v>
       </c>
-      <c r="AM5" s="39" t="s">
+      <c r="AM5" s="35" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="6" spans="1:39" ht="67.5">
+    <row r="6" spans="1:39" ht="68">
       <c r="A6" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="35" t="s">
         <v>491</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="35" t="s">
         <v>490</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D6" s="35" t="s">
         <v>500</v>
       </c>
       <c r="E6" s="11">
@@ -4656,7 +4660,7 @@
       <c r="L6" s="11" t="s">
         <v>515</v>
       </c>
-      <c r="M6" s="33" t="s">
+      <c r="M6" s="29" t="s">
         <v>518</v>
       </c>
       <c r="N6" s="11">
@@ -4680,7 +4684,7 @@
       <c r="W6" s="11" t="s">
         <v>516</v>
       </c>
-      <c r="X6" s="33" t="s">
+      <c r="X6" s="29" t="s">
         <v>523</v>
       </c>
       <c r="Y6" s="11">
@@ -4707,33 +4711,33 @@
       <c r="AG6" s="18">
         <v>0.3</v>
       </c>
-      <c r="AH6" s="33" t="s">
+      <c r="AH6" s="29" t="s">
         <v>527</v>
       </c>
       <c r="AI6" s="11">
         <v>10</v>
       </c>
-      <c r="AJ6" s="39">
+      <c r="AJ6" s="35">
         <v>5</v>
       </c>
-      <c r="AK6" s="39">
+      <c r="AK6" s="35">
         <v>2</v>
       </c>
-      <c r="AL6" s="39">
+      <c r="AL6" s="35">
         <v>4</v>
       </c>
-      <c r="AM6" s="39">
+      <c r="AM6" s="35">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:39" ht="101.25">
-      <c r="B7" s="39" t="s">
+    <row r="7" spans="1:39" ht="102">
+      <c r="B7" s="35" t="s">
         <v>492</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="35" t="s">
         <v>496</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="35" t="s">
         <v>501</v>
       </c>
       <c r="E7" s="28">
@@ -4760,7 +4764,7 @@
       <c r="L7" s="11" t="s">
         <v>510</v>
       </c>
-      <c r="M7" s="33" t="s">
+      <c r="M7" s="29" t="s">
         <v>524</v>
       </c>
       <c r="N7" s="11">
@@ -4781,33 +4785,33 @@
       <c r="V7" s="18"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="18"/>
-      <c r="AH7" s="33" t="s">
+      <c r="AH7" s="29" t="s">
         <v>528</v>
       </c>
       <c r="AI7" s="11">
         <v>20</v>
       </c>
-      <c r="AJ7" s="39">
+      <c r="AJ7" s="35">
         <v>5</v>
       </c>
-      <c r="AK7" s="39">
+      <c r="AK7" s="35">
         <v>3</v>
       </c>
-      <c r="AL7" s="39">
+      <c r="AL7" s="35">
         <v>3</v>
       </c>
-      <c r="AM7" s="39">
+      <c r="AM7" s="35">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:39" ht="84.4">
-      <c r="B8" s="39" t="s">
+    <row r="8" spans="1:39" ht="85">
+      <c r="B8" s="35" t="s">
         <v>493</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="35" t="s">
         <v>497</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="35" t="s">
         <v>502</v>
       </c>
       <c r="E8" s="28">
@@ -4834,7 +4838,7 @@
       <c r="L8" s="28" t="s">
         <v>517</v>
       </c>
-      <c r="M8" s="33" t="s">
+      <c r="M8" s="29" t="s">
         <v>525</v>
       </c>
       <c r="N8" s="11">
@@ -4856,38 +4860,38 @@
       <c r="W8" s="11" t="s">
         <v>511</v>
       </c>
-      <c r="X8" s="33" t="s">
+      <c r="X8" s="29" t="s">
         <v>526</v>
       </c>
       <c r="AF8" s="18"/>
       <c r="AG8" s="18"/>
-      <c r="AH8" s="33" t="s">
+      <c r="AH8" s="29" t="s">
         <v>529</v>
       </c>
       <c r="AI8" s="11">
         <v>30</v>
       </c>
-      <c r="AJ8" s="39">
+      <c r="AJ8" s="35">
         <v>5</v>
       </c>
-      <c r="AK8" s="39">
+      <c r="AK8" s="35">
         <v>3</v>
       </c>
-      <c r="AL8" s="39">
+      <c r="AL8" s="35">
         <v>2</v>
       </c>
-      <c r="AM8" s="39">
+      <c r="AM8" s="35">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:39" s="28" customFormat="1" ht="67.5">
-      <c r="B9" s="39" t="s">
+    <row r="9" spans="1:39" s="28" customFormat="1" ht="68">
+      <c r="B9" s="35" t="s">
         <v>494</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="35" t="s">
         <v>498</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="35" t="s">
         <v>503</v>
       </c>
       <c r="E9" s="28">
@@ -4914,7 +4918,7 @@
       <c r="L9" s="28" t="s">
         <v>512</v>
       </c>
-      <c r="M9" s="33" t="s">
+      <c r="M9" s="29" t="s">
         <v>534</v>
       </c>
       <c r="N9" s="28">
@@ -4935,33 +4939,33 @@
       <c r="V9" s="18"/>
       <c r="AF9" s="18"/>
       <c r="AG9" s="18"/>
-      <c r="AH9" s="33" t="s">
+      <c r="AH9" s="29" t="s">
         <v>530</v>
       </c>
       <c r="AI9" s="28">
         <v>40</v>
       </c>
-      <c r="AJ9" s="39">
+      <c r="AJ9" s="35">
         <v>5</v>
       </c>
-      <c r="AK9" s="39">
+      <c r="AK9" s="35">
         <v>3</v>
       </c>
-      <c r="AL9" s="39">
+      <c r="AL9" s="35">
         <v>4</v>
       </c>
-      <c r="AM9" s="39">
+      <c r="AM9" s="35">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:39" s="28" customFormat="1" ht="67.5">
-      <c r="B10" s="39" t="s">
+    <row r="10" spans="1:39" s="28" customFormat="1" ht="68">
+      <c r="B10" s="35" t="s">
         <v>495</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="35" t="s">
         <v>499</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="35" t="s">
         <v>504</v>
       </c>
       <c r="E10" s="28">
@@ -4988,7 +4992,7 @@
       <c r="L10" s="28" t="s">
         <v>513</v>
       </c>
-      <c r="M10" s="33" t="s">
+      <c r="M10" s="29" t="s">
         <v>525</v>
       </c>
       <c r="N10" s="28">
@@ -5010,7 +5014,7 @@
       <c r="W10" s="28" t="s">
         <v>514</v>
       </c>
-      <c r="X10" s="33" t="s">
+      <c r="X10" s="29" t="s">
         <v>531</v>
       </c>
       <c r="Y10" s="28">
@@ -5037,26 +5041,26 @@
       <c r="AG10" s="18">
         <v>1</v>
       </c>
-      <c r="AH10" s="33" t="s">
+      <c r="AH10" s="29" t="s">
         <v>533</v>
       </c>
       <c r="AI10" s="28">
         <v>50</v>
       </c>
-      <c r="AJ10" s="39">
+      <c r="AJ10" s="35">
         <v>5</v>
       </c>
-      <c r="AK10" s="39">
+      <c r="AK10" s="35">
         <v>4</v>
       </c>
-      <c r="AL10" s="39">
+      <c r="AL10" s="35">
         <v>4</v>
       </c>
-      <c r="AM10" s="39">
+      <c r="AM10" s="35">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:39" ht="33.75">
+    <row r="12" spans="1:39" ht="34">
       <c r="A12" s="11" t="s">
         <v>186</v>
       </c>
@@ -5096,7 +5100,7 @@
       <c r="M12" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="N12" s="33" t="s">
+      <c r="N12" s="29" t="s">
         <v>519</v>
       </c>
       <c r="O12" s="11" t="s">
@@ -5349,12 +5353,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A705E06-4C8A-43EB-9784-7D906D56BEF6}">
   <dimension ref="A1:O41"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="10.5" style="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="12" width="15.5625" style="19" customWidth="1"/>
-    <col min="13" max="13" width="16.875" style="19" bestFit="1" customWidth="1"/>
-    <col min="14" max="36" width="15.5625" style="19" customWidth="1"/>
+    <col min="2" max="12" width="15.58203125" style="19" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="14" max="36" width="15.58203125" style="19" customWidth="1"/>
     <col min="37" max="16384" width="9" style="19"/>
   </cols>
   <sheetData>
@@ -5364,10 +5368,10 @@
       </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="49" t="s">
         <v>264</v>
       </c>
-      <c r="C2" s="32"/>
+      <c r="C2" s="49"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="19" t="s">
@@ -5406,13 +5410,13 @@
       <c r="L4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="32" t="s">
         <v>288</v>
       </c>
-      <c r="N4" s="36" t="s">
+      <c r="N4" s="32" t="s">
         <v>289</v>
       </c>
-      <c r="O4" s="36" t="s">
+      <c r="O4" s="32" t="s">
         <v>289</v>
       </c>
     </row>
@@ -5423,7 +5427,7 @@
       <c r="B5" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="30" t="s">
         <v>265</v>
       </c>
       <c r="D5" s="19" t="s">
@@ -5453,13 +5457,13 @@
       <c r="L5" s="19" t="s">
         <v>274</v>
       </c>
-      <c r="M5" s="37" t="s">
+      <c r="M5" s="33" t="s">
         <v>286</v>
       </c>
-      <c r="N5" s="36" t="s">
+      <c r="N5" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="O5" s="36" t="s">
+      <c r="O5" s="32" t="s">
         <v>290</v>
       </c>
     </row>
@@ -5494,9 +5498,9 @@
       <c r="J6" s="19">
         <v>6</v>
       </c>
-      <c r="M6" s="37"/>
-      <c r="N6" s="37"/>
-      <c r="O6" s="37"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="33"/>
+      <c r="O6" s="33"/>
     </row>
     <row r="7" spans="1:15">
       <c r="B7" s="19">
@@ -5526,9 +5530,9 @@
       <c r="J7" s="19">
         <v>6</v>
       </c>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="33"/>
     </row>
     <row r="8" spans="1:15">
       <c r="B8" s="19">
@@ -5558,9 +5562,9 @@
       <c r="J8" s="19">
         <v>6</v>
       </c>
-      <c r="M8" s="37"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="33"/>
+      <c r="O8" s="33"/>
     </row>
     <row r="9" spans="1:15">
       <c r="B9" s="19">
@@ -5578,9 +5582,9 @@
       <c r="F9" s="19">
         <v>3</v>
       </c>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33"/>
     </row>
     <row r="10" spans="1:15">
       <c r="B10" s="19">
@@ -5604,9 +5608,9 @@
       <c r="H10" s="19">
         <v>6</v>
       </c>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="33"/>
     </row>
     <row r="11" spans="1:15">
       <c r="B11" s="19">
@@ -5630,9 +5634,9 @@
       <c r="H11" s="19">
         <v>5</v>
       </c>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="33"/>
+      <c r="O11" s="33"/>
     </row>
     <row r="12" spans="1:15">
       <c r="B12" s="19">
@@ -5662,9 +5666,9 @@
       <c r="J12" s="19">
         <v>6</v>
       </c>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="33"/>
+      <c r="O12" s="33"/>
     </row>
     <row r="13" spans="1:15">
       <c r="B13" s="19">
@@ -5700,9 +5704,9 @@
       <c r="L13" s="19">
         <v>5</v>
       </c>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
+      <c r="M13" s="33"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="33"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="19" t="s">
@@ -5711,43 +5715,43 @@
       <c r="B15" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="35" t="s">
+      <c r="C15" s="31" t="s">
         <v>291</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="31" t="s">
         <v>291</v>
       </c>
       <c r="F15" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="G15" s="35" t="s">
+      <c r="G15" s="31" t="s">
         <v>291</v>
       </c>
       <c r="H15" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="I15" s="35" t="s">
+      <c r="I15" s="31" t="s">
         <v>291</v>
       </c>
       <c r="J15" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="K15" s="35" t="s">
+      <c r="K15" s="31" t="s">
         <v>291</v>
       </c>
       <c r="L15" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="M15" s="34" t="s">
+      <c r="M15" s="30" t="s">
         <v>292</v>
       </c>
-      <c r="N15" s="34" t="s">
+      <c r="N15" s="30" t="s">
         <v>293</v>
       </c>
-      <c r="O15" s="34" t="s">
+      <c r="O15" s="30" t="s">
         <v>294</v>
       </c>
     </row>
@@ -5909,24 +5913,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DEBB537-D2E1-4D20-A494-C05A81D52093}">
   <dimension ref="A1:Z40"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="10.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="15.5625" style="11" customWidth="1"/>
-    <col min="5" max="5" width="33.4375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="15.58203125" style="11" customWidth="1"/>
+    <col min="5" max="5" width="33.4140625" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="50" style="11" customWidth="1"/>
-    <col min="7" max="7" width="15.5625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="27.6875" style="11" customWidth="1"/>
-    <col min="9" max="12" width="15.5625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="15.58203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="27.6640625" style="11" customWidth="1"/>
+    <col min="9" max="12" width="15.58203125" style="11" customWidth="1"/>
     <col min="13" max="13" width="37.75" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="44.9375" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="44.9140625" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="25" style="11" customWidth="1"/>
-    <col min="16" max="16" width="24.5625" style="11" customWidth="1"/>
-    <col min="17" max="17" width="24.3125" style="11" customWidth="1"/>
-    <col min="18" max="18" width="22.8125" style="11" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.5625" style="11" customWidth="1"/>
-    <col min="20" max="20" width="22.8125" style="11" bestFit="1" customWidth="1"/>
-    <col min="21" max="62" width="15.5625" style="11" customWidth="1"/>
+    <col min="16" max="16" width="24.58203125" style="11" customWidth="1"/>
+    <col min="17" max="17" width="24.33203125" style="11" customWidth="1"/>
+    <col min="18" max="18" width="22.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.58203125" style="11" customWidth="1"/>
+    <col min="20" max="20" width="22.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="21" max="62" width="15.58203125" style="11" customWidth="1"/>
     <col min="63" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
@@ -5936,30 +5940,30 @@
       </c>
     </row>
     <row r="2" spans="1:26">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="46" t="s">
         <v>223</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
     </row>
     <row r="4" spans="1:26">
       <c r="A4" s="7" t="s">
         <v>182</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>19</v>
@@ -6118,16 +6122,16 @@
       <c r="A6" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="35" t="s">
         <v>331</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="35" t="s">
         <v>329</v>
       </c>
-      <c r="D6" s="39">
-        <v>1</v>
-      </c>
-      <c r="E6" s="39" t="s">
+      <c r="D6" s="35">
+        <v>1</v>
+      </c>
+      <c r="E6" s="35" t="s">
         <v>344</v>
       </c>
       <c r="F6" s="28" t="s">
@@ -6151,52 +6155,52 @@
       <c r="L6" s="28"/>
       <c r="M6" s="28"/>
       <c r="N6" s="28"/>
-      <c r="O6" s="46">
-        <v>1</v>
-      </c>
-      <c r="P6" s="46"/>
-      <c r="Q6" s="46">
-        <v>1</v>
-      </c>
-      <c r="R6" s="46" t="str">
+      <c r="O6" s="42">
+        <v>1</v>
+      </c>
+      <c r="P6" s="42"/>
+      <c r="Q6" s="42">
+        <v>1</v>
+      </c>
+      <c r="R6" s="42" t="str">
         <f>IFERROR(IF(ROUND(P6*1.2,1)=0,"",ROUND(P6*1.2,1)),"")</f>
         <v/>
       </c>
-      <c r="S6" s="46">
-        <v>1</v>
-      </c>
-      <c r="T6" s="46" t="str">
+      <c r="S6" s="42">
+        <v>1</v>
+      </c>
+      <c r="T6" s="42" t="str">
         <f>IFERROR(IF(ROUND(R6*1.2,1)=0,"",ROUND(R6*1.2,1)),"")</f>
         <v/>
       </c>
-      <c r="U6" s="46">
-        <v>1</v>
-      </c>
-      <c r="V6" s="46" t="str">
+      <c r="U6" s="42">
+        <v>1</v>
+      </c>
+      <c r="V6" s="42" t="str">
         <f>IFERROR(IF(ROUND(T6*1.2,1)=0,"",ROUND(T6*1.2,1)),"")</f>
         <v/>
       </c>
-      <c r="W6" s="46">
-        <v>1</v>
-      </c>
-      <c r="X6" s="39"/>
-      <c r="Y6" s="39"/>
-      <c r="Z6" s="39" t="s">
+      <c r="W6" s="42">
+        <v>1</v>
+      </c>
+      <c r="X6" s="35"/>
+      <c r="Y6" s="35"/>
+      <c r="Z6" s="35" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="7" spans="1:26" s="28" customFormat="1">
       <c r="A7" s="7"/>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="35" t="s">
         <v>333</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="35" t="s">
         <v>329</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="35">
         <v>2</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="E7" s="35" t="s">
         <v>346</v>
       </c>
       <c r="F7" s="28" t="s">
@@ -6223,53 +6227,53 @@
       <c r="M7" s="28">
         <v>0</v>
       </c>
-      <c r="O7" s="46">
-        <v>1</v>
-      </c>
-      <c r="P7" s="46">
+      <c r="O7" s="42">
+        <v>1</v>
+      </c>
+      <c r="P7" s="42">
         <v>0.2</v>
       </c>
-      <c r="Q7" s="46">
-        <v>1</v>
-      </c>
-      <c r="R7" s="46">
+      <c r="Q7" s="42">
+        <v>1</v>
+      </c>
+      <c r="R7" s="42">
         <v>0.2</v>
       </c>
-      <c r="S7" s="46">
-        <v>1</v>
-      </c>
-      <c r="T7" s="46">
+      <c r="S7" s="42">
+        <v>1</v>
+      </c>
+      <c r="T7" s="42">
         <v>0.2</v>
       </c>
-      <c r="U7" s="46">
-        <v>1</v>
-      </c>
-      <c r="V7" s="46">
+      <c r="U7" s="42">
+        <v>1</v>
+      </c>
+      <c r="V7" s="42">
         <v>0.2</v>
       </c>
-      <c r="W7" s="46">
-        <v>1</v>
-      </c>
-      <c r="X7" s="46">
+      <c r="W7" s="42">
+        <v>1</v>
+      </c>
+      <c r="X7" s="42">
         <v>0.2</v>
       </c>
-      <c r="Y7" s="39"/>
-      <c r="Z7" s="39" t="s">
+      <c r="Y7" s="35"/>
+      <c r="Z7" s="35" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="8" spans="1:26" s="28" customFormat="1">
       <c r="A8" s="7"/>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="35" t="s">
         <v>334</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="35" t="s">
         <v>329</v>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="35">
         <v>3</v>
       </c>
-      <c r="E8" s="39" t="s">
+      <c r="E8" s="35" t="s">
         <v>348</v>
       </c>
       <c r="F8" s="28" t="s">
@@ -6299,103 +6303,103 @@
       <c r="N8" s="28">
         <v>1</v>
       </c>
-      <c r="O8" s="46">
+      <c r="O8" s="42">
         <v>0.6</v>
       </c>
-      <c r="P8" s="46">
+      <c r="P8" s="42">
         <v>0.8</v>
       </c>
-      <c r="Q8" s="46">
+      <c r="Q8" s="42">
         <v>0.6</v>
       </c>
-      <c r="R8" s="46">
+      <c r="R8" s="42">
         <v>0.8</v>
       </c>
-      <c r="S8" s="46">
+      <c r="S8" s="42">
         <v>0.6</v>
       </c>
-      <c r="T8" s="46">
+      <c r="T8" s="42">
         <v>0.8</v>
       </c>
-      <c r="U8" s="46">
+      <c r="U8" s="42">
         <v>0.6</v>
       </c>
-      <c r="V8" s="46">
+      <c r="V8" s="42">
         <v>0.8</v>
       </c>
-      <c r="W8" s="46">
+      <c r="W8" s="42">
         <v>0.6</v>
       </c>
-      <c r="X8" s="46">
+      <c r="X8" s="42">
         <v>0.8</v>
       </c>
-      <c r="Y8" s="39"/>
-      <c r="Z8" s="39" t="s">
+      <c r="Y8" s="35"/>
+      <c r="Z8" s="35" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:26" s="28" customFormat="1">
       <c r="A9" s="7"/>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="35" t="s">
         <v>335</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="35" t="s">
         <v>329</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="35">
         <v>4</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="E9" s="35" t="s">
         <v>350</v>
       </c>
-      <c r="F9" s="39" t="s">
+      <c r="F9" s="35" t="s">
         <v>394</v>
       </c>
-      <c r="G9" s="39">
-        <v>0</v>
-      </c>
-      <c r="H9" s="39">
-        <v>0</v>
-      </c>
-      <c r="I9" s="39">
-        <v>0</v>
-      </c>
-      <c r="J9" s="39">
-        <v>0</v>
-      </c>
-      <c r="K9" s="39">
+      <c r="G9" s="35">
+        <v>0</v>
+      </c>
+      <c r="H9" s="35">
+        <v>0</v>
+      </c>
+      <c r="I9" s="35">
+        <v>0</v>
+      </c>
+      <c r="J9" s="35">
+        <v>0</v>
+      </c>
+      <c r="K9" s="35">
         <v>2</v>
       </c>
-      <c r="L9" s="39"/>
-      <c r="M9" s="39"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="46"/>
-      <c r="P9" s="46"/>
-      <c r="Q9" s="46"/>
-      <c r="R9" s="46"/>
-      <c r="S9" s="46"/>
-      <c r="T9" s="46"/>
-      <c r="U9" s="46"/>
-      <c r="V9" s="46"/>
-      <c r="W9" s="46"/>
-      <c r="X9" s="46"/>
-      <c r="Y9" s="39"/>
-      <c r="Z9" s="39" t="s">
+      <c r="L9" s="35"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="42"/>
+      <c r="P9" s="42"/>
+      <c r="Q9" s="42"/>
+      <c r="R9" s="42"/>
+      <c r="S9" s="42"/>
+      <c r="T9" s="42"/>
+      <c r="U9" s="42"/>
+      <c r="V9" s="42"/>
+      <c r="W9" s="42"/>
+      <c r="X9" s="42"/>
+      <c r="Y9" s="35"/>
+      <c r="Z9" s="35" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:26" s="28" customFormat="1">
       <c r="A10" s="7"/>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="35" t="s">
         <v>337</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="35" t="s">
         <v>329</v>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="35">
         <v>5</v>
       </c>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="35" t="s">
         <v>345</v>
       </c>
       <c r="F10" s="28" t="s">
@@ -6416,54 +6420,54 @@
       <c r="K10" s="28">
         <v>0</v>
       </c>
-      <c r="O10" s="46">
+      <c r="O10" s="42">
         <v>1.2</v>
       </c>
-      <c r="P10" s="46"/>
-      <c r="Q10" s="46">
+      <c r="P10" s="42"/>
+      <c r="Q10" s="42">
         <v>1.2</v>
       </c>
-      <c r="R10" s="46" t="str">
+      <c r="R10" s="42" t="str">
         <f>IFERROR(IF(ROUND(P10*1.2,1)=0,"",ROUND(P10*1.2,1)),"")</f>
         <v/>
       </c>
-      <c r="S10" s="46">
+      <c r="S10" s="42">
         <v>1.2</v>
       </c>
-      <c r="T10" s="46" t="str">
+      <c r="T10" s="42" t="str">
         <f>IFERROR(IF(ROUND(R10*1.2,1)=0,"",ROUND(R10*1.2,1)),"")</f>
         <v/>
       </c>
-      <c r="U10" s="46">
+      <c r="U10" s="42">
         <v>1.2</v>
       </c>
-      <c r="V10" s="46" t="str">
+      <c r="V10" s="42" t="str">
         <f>IFERROR(IF(ROUND(T10*1.2,1)=0,"",ROUND(T10*1.2,1)),"")</f>
         <v/>
       </c>
-      <c r="W10" s="46">
+      <c r="W10" s="42">
         <v>1.2</v>
       </c>
-      <c r="X10" s="46"/>
-      <c r="Y10" s="39" t="s">
+      <c r="X10" s="42"/>
+      <c r="Y10" s="35" t="s">
         <v>331</v>
       </c>
-      <c r="Z10" s="39" t="s">
+      <c r="Z10" s="35" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="11" spans="1:26" s="28" customFormat="1">
       <c r="A11" s="7"/>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="35" t="s">
         <v>339</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="35" t="s">
         <v>329</v>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="35">
         <v>6</v>
       </c>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="35" t="s">
         <v>347</v>
       </c>
       <c r="F11" s="28" t="s">
@@ -6490,55 +6494,55 @@
       <c r="M11" s="28">
         <v>0</v>
       </c>
-      <c r="O11" s="46">
+      <c r="O11" s="42">
         <v>1.2</v>
       </c>
-      <c r="P11" s="46">
+      <c r="P11" s="42">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="46">
+      <c r="Q11" s="42">
         <v>1.2</v>
       </c>
-      <c r="R11" s="46">
+      <c r="R11" s="42">
         <v>0.2</v>
       </c>
-      <c r="S11" s="46">
+      <c r="S11" s="42">
         <v>1.2</v>
       </c>
-      <c r="T11" s="46">
+      <c r="T11" s="42">
         <v>0.2</v>
       </c>
-      <c r="U11" s="46">
+      <c r="U11" s="42">
         <v>1.2</v>
       </c>
-      <c r="V11" s="46">
+      <c r="V11" s="42">
         <v>0.2</v>
       </c>
-      <c r="W11" s="46">
+      <c r="W11" s="42">
         <v>1.2</v>
       </c>
-      <c r="X11" s="46">
+      <c r="X11" s="42">
         <v>0.2</v>
       </c>
-      <c r="Y11" s="39" t="s">
+      <c r="Y11" s="35" t="s">
         <v>333</v>
       </c>
-      <c r="Z11" s="39" t="s">
+      <c r="Z11" s="35" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="12" spans="1:26" s="28" customFormat="1">
       <c r="A12" s="7"/>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="35" t="s">
         <v>329</v>
       </c>
-      <c r="D12" s="39">
+      <c r="D12" s="35">
         <v>7</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="35" t="s">
         <v>349</v>
       </c>
       <c r="F12" s="28" t="s">
@@ -6568,107 +6572,107 @@
       <c r="N12" s="28">
         <v>1</v>
       </c>
-      <c r="O12" s="46">
+      <c r="O12" s="42">
         <v>0.7</v>
       </c>
-      <c r="P12" s="46">
+      <c r="P12" s="42">
         <v>0.9</v>
       </c>
-      <c r="Q12" s="46">
+      <c r="Q12" s="42">
         <v>0.7</v>
       </c>
-      <c r="R12" s="46">
+      <c r="R12" s="42">
         <v>0.9</v>
       </c>
-      <c r="S12" s="46">
+      <c r="S12" s="42">
         <v>0.7</v>
       </c>
-      <c r="T12" s="46">
+      <c r="T12" s="42">
         <v>0.9</v>
       </c>
-      <c r="U12" s="46">
+      <c r="U12" s="42">
         <v>0.7</v>
       </c>
-      <c r="V12" s="46">
+      <c r="V12" s="42">
         <v>0.9</v>
       </c>
-      <c r="W12" s="46">
+      <c r="W12" s="42">
         <v>0.7</v>
       </c>
-      <c r="X12" s="46">
+      <c r="X12" s="42">
         <v>0.9</v>
       </c>
-      <c r="Y12" s="39" t="s">
+      <c r="Y12" s="35" t="s">
         <v>334</v>
       </c>
-      <c r="Z12" s="39" t="s">
+      <c r="Z12" s="35" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="28" customFormat="1">
       <c r="A13" s="7"/>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="35" t="s">
         <v>343</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="35" t="s">
         <v>329</v>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="35">
         <v>8</v>
       </c>
-      <c r="E13" s="39" t="s">
+      <c r="E13" s="35" t="s">
         <v>351</v>
       </c>
-      <c r="F13" s="39" t="s">
+      <c r="F13" s="35" t="s">
         <v>394</v>
       </c>
-      <c r="G13" s="39">
-        <v>0</v>
-      </c>
-      <c r="H13" s="39">
-        <v>0</v>
-      </c>
-      <c r="I13" s="39">
-        <v>0</v>
-      </c>
-      <c r="J13" s="39">
-        <v>0</v>
-      </c>
-      <c r="K13" s="39">
+      <c r="G13" s="35">
+        <v>0</v>
+      </c>
+      <c r="H13" s="35">
+        <v>0</v>
+      </c>
+      <c r="I13" s="35">
+        <v>0</v>
+      </c>
+      <c r="J13" s="35">
+        <v>0</v>
+      </c>
+      <c r="K13" s="35">
         <v>2</v>
       </c>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="39"/>
-      <c r="O13" s="46"/>
-      <c r="P13" s="46"/>
-      <c r="Q13" s="46"/>
-      <c r="R13" s="46"/>
-      <c r="S13" s="46"/>
-      <c r="T13" s="46"/>
-      <c r="U13" s="46"/>
-      <c r="V13" s="46"/>
-      <c r="W13" s="46"/>
-      <c r="X13" s="46"/>
-      <c r="Y13" s="39" t="s">
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="42"/>
+      <c r="R13" s="42"/>
+      <c r="S13" s="42"/>
+      <c r="T13" s="42"/>
+      <c r="U13" s="42"/>
+      <c r="V13" s="42"/>
+      <c r="W13" s="42"/>
+      <c r="X13" s="42"/>
+      <c r="Y13" s="35" t="s">
         <v>335</v>
       </c>
-      <c r="Z13" s="39" t="s">
+      <c r="Z13" s="35" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="14" spans="1:26" s="28" customFormat="1">
       <c r="A14" s="7"/>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="35" t="s">
         <v>396</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="35" t="s">
         <v>411</v>
       </c>
-      <c r="D14" s="39">
-        <v>1</v>
-      </c>
-      <c r="E14" s="39" t="s">
+      <c r="D14" s="35">
+        <v>1</v>
+      </c>
+      <c r="E14" s="35" t="s">
         <v>412</v>
       </c>
       <c r="F14" s="28" t="s">
@@ -6689,52 +6693,52 @@
       <c r="K14" s="28">
         <v>0</v>
       </c>
-      <c r="O14" s="46">
-        <v>1</v>
-      </c>
-      <c r="P14" s="46"/>
-      <c r="Q14" s="46">
-        <v>1</v>
-      </c>
-      <c r="R14" s="46" t="str">
+      <c r="O14" s="42">
+        <v>1</v>
+      </c>
+      <c r="P14" s="42"/>
+      <c r="Q14" s="42">
+        <v>1</v>
+      </c>
+      <c r="R14" s="42" t="str">
         <f>IFERROR(IF(ROUND(P14*1.2,1)=0,"",ROUND(P14*1.2,1)),"")</f>
         <v/>
       </c>
-      <c r="S14" s="46">
-        <v>1</v>
-      </c>
-      <c r="T14" s="46" t="str">
+      <c r="S14" s="42">
+        <v>1</v>
+      </c>
+      <c r="T14" s="42" t="str">
         <f>IFERROR(IF(ROUND(R14*1.2,1)=0,"",ROUND(R14*1.2,1)),"")</f>
         <v/>
       </c>
-      <c r="U14" s="46">
-        <v>1</v>
-      </c>
-      <c r="V14" s="46" t="str">
+      <c r="U14" s="42">
+        <v>1</v>
+      </c>
+      <c r="V14" s="42" t="str">
         <f>IFERROR(IF(ROUND(T14*1.2,1)=0,"",ROUND(T14*1.2,1)),"")</f>
         <v/>
       </c>
-      <c r="W14" s="46">
-        <v>1</v>
-      </c>
-      <c r="X14" s="46"/>
-      <c r="Y14" s="39"/>
-      <c r="Z14" s="39" t="s">
+      <c r="W14" s="42">
+        <v>1</v>
+      </c>
+      <c r="X14" s="42"/>
+      <c r="Y14" s="35"/>
+      <c r="Z14" s="35" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="15" spans="1:26" s="28" customFormat="1">
       <c r="A15" s="7"/>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="35" t="s">
         <v>398</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="35" t="s">
         <v>411</v>
       </c>
-      <c r="D15" s="39">
+      <c r="D15" s="35">
         <v>2</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="E15" s="35" t="s">
         <v>414</v>
       </c>
       <c r="F15" s="28" t="s">
@@ -6755,7 +6759,7 @@
       <c r="K15" s="28">
         <v>0</v>
       </c>
-      <c r="L15" s="39" t="s">
+      <c r="L15" s="35" t="s">
         <v>488</v>
       </c>
       <c r="M15" s="28">
@@ -6764,53 +6768,53 @@
       <c r="N15" s="28">
         <v>1</v>
       </c>
-      <c r="O15" s="46">
+      <c r="O15" s="42">
         <v>0.9</v>
       </c>
-      <c r="P15" s="46">
+      <c r="P15" s="42">
         <v>0.3</v>
       </c>
-      <c r="Q15" s="46">
+      <c r="Q15" s="42">
         <v>0.9</v>
       </c>
-      <c r="R15" s="46">
+      <c r="R15" s="42">
         <v>0.3</v>
       </c>
-      <c r="S15" s="46">
+      <c r="S15" s="42">
         <v>0.9</v>
       </c>
-      <c r="T15" s="46">
+      <c r="T15" s="42">
         <v>0.3</v>
       </c>
-      <c r="U15" s="46">
+      <c r="U15" s="42">
         <v>0.9</v>
       </c>
-      <c r="V15" s="46">
+      <c r="V15" s="42">
         <v>0.3</v>
       </c>
-      <c r="W15" s="46">
+      <c r="W15" s="42">
         <v>0.9</v>
       </c>
-      <c r="X15" s="46">
+      <c r="X15" s="42">
         <v>0.3</v>
       </c>
-      <c r="Y15" s="39"/>
-      <c r="Z15" s="39" t="s">
+      <c r="Y15" s="35"/>
+      <c r="Z15" s="35" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="16" spans="1:26" s="28" customFormat="1">
       <c r="A16" s="7"/>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="35" t="s">
         <v>400</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="35" t="s">
         <v>411</v>
       </c>
-      <c r="D16" s="39">
+      <c r="D16" s="35">
         <v>3</v>
       </c>
-      <c r="E16" s="39" t="s">
+      <c r="E16" s="35" t="s">
         <v>416</v>
       </c>
       <c r="F16" s="28" t="s">
@@ -6837,125 +6841,125 @@
       <c r="M16" s="28">
         <v>0</v>
       </c>
-      <c r="O16" s="46">
+      <c r="O16" s="42">
         <v>0.6</v>
       </c>
-      <c r="P16" s="46"/>
-      <c r="Q16" s="46">
+      <c r="P16" s="42"/>
+      <c r="Q16" s="42">
         <v>0.6</v>
       </c>
-      <c r="R16" s="46" t="str">
+      <c r="R16" s="42" t="str">
         <f t="shared" ref="R16" si="0">IFERROR(IF(ROUND(P16*1.2,1)=0,"",ROUND(P16*1.2,1)),"")</f>
         <v/>
       </c>
-      <c r="S16" s="46">
+      <c r="S16" s="42">
         <v>0.6</v>
       </c>
-      <c r="T16" s="46" t="str">
+      <c r="T16" s="42" t="str">
         <f t="shared" ref="T16" si="1">IFERROR(IF(ROUND(R16*1.2,1)=0,"",ROUND(R16*1.2,1)),"")</f>
         <v/>
       </c>
-      <c r="U16" s="46">
+      <c r="U16" s="42">
         <v>0.6</v>
       </c>
-      <c r="V16" s="46" t="str">
+      <c r="V16" s="42" t="str">
         <f t="shared" ref="V16" si="2">IFERROR(IF(ROUND(T16*1.2,1)=0,"",ROUND(T16*1.2,1)),"")</f>
         <v/>
       </c>
-      <c r="W16" s="46">
+      <c r="W16" s="42">
         <v>0.6</v>
       </c>
-      <c r="X16" s="46" t="str">
+      <c r="X16" s="42" t="str">
         <f t="shared" ref="X16" si="3">IFERROR(IF(ROUND(V16*1.2,1)=0,"",ROUND(V16*1.2,1)),"")</f>
         <v/>
       </c>
-      <c r="Y16" s="39"/>
-      <c r="Z16" s="39" t="s">
+      <c r="Y16" s="35"/>
+      <c r="Z16" s="35" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="17" spans="1:26" s="28" customFormat="1">
       <c r="A17" s="7"/>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="35" t="s">
         <v>402</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="35" t="s">
         <v>411</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="35">
         <v>4</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="E17" s="35" t="s">
         <v>418</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="35" t="s">
         <v>422</v>
       </c>
-      <c r="G17" s="39">
-        <v>0</v>
-      </c>
-      <c r="H17" s="39">
-        <v>0</v>
-      </c>
-      <c r="I17" s="39">
-        <v>1</v>
-      </c>
-      <c r="J17" s="39">
-        <v>1</v>
-      </c>
-      <c r="K17" s="39">
+      <c r="G17" s="35">
+        <v>0</v>
+      </c>
+      <c r="H17" s="35">
+        <v>0</v>
+      </c>
+      <c r="I17" s="35">
+        <v>1</v>
+      </c>
+      <c r="J17" s="35">
+        <v>1</v>
+      </c>
+      <c r="K17" s="35">
         <v>2</v>
       </c>
-      <c r="L17" s="39"/>
-      <c r="M17" s="39"/>
-      <c r="N17" s="39"/>
-      <c r="O17" s="46">
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="42">
         <v>0.6</v>
       </c>
-      <c r="P17" s="46">
+      <c r="P17" s="42">
         <v>0.05</v>
       </c>
-      <c r="Q17" s="46">
+      <c r="Q17" s="42">
         <v>0.6</v>
       </c>
-      <c r="R17" s="46">
+      <c r="R17" s="42">
         <v>0.05</v>
       </c>
-      <c r="S17" s="46">
+      <c r="S17" s="42">
         <v>0.6</v>
       </c>
-      <c r="T17" s="46">
+      <c r="T17" s="42">
         <v>0.05</v>
       </c>
-      <c r="U17" s="46">
+      <c r="U17" s="42">
         <v>0.6</v>
       </c>
-      <c r="V17" s="46">
+      <c r="V17" s="42">
         <v>0.05</v>
       </c>
-      <c r="W17" s="46">
+      <c r="W17" s="42">
         <v>0.6</v>
       </c>
-      <c r="X17" s="46">
+      <c r="X17" s="42">
         <v>0.05</v>
       </c>
-      <c r="Y17" s="39"/>
-      <c r="Z17" s="39" t="s">
+      <c r="Y17" s="35"/>
+      <c r="Z17" s="35" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="18" spans="1:26" s="28" customFormat="1">
       <c r="A18" s="7"/>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="35" t="s">
         <v>404</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="35" t="s">
         <v>411</v>
       </c>
-      <c r="D18" s="39">
+      <c r="D18" s="35">
         <v>5</v>
       </c>
-      <c r="E18" s="39" t="s">
+      <c r="E18" s="35" t="s">
         <v>413</v>
       </c>
       <c r="F18" s="28" t="s">
@@ -6976,54 +6980,54 @@
       <c r="K18" s="28">
         <v>0</v>
       </c>
-      <c r="O18" s="46">
+      <c r="O18" s="42">
         <v>1.2</v>
       </c>
-      <c r="P18" s="46"/>
-      <c r="Q18" s="46">
+      <c r="P18" s="42"/>
+      <c r="Q18" s="42">
         <v>1.2</v>
       </c>
-      <c r="R18" s="46" t="str">
+      <c r="R18" s="42" t="str">
         <f>IFERROR(IF(ROUND(P18*1.2,1)=0,"",ROUND(P18*1.2,1)),"")</f>
         <v/>
       </c>
-      <c r="S18" s="46">
+      <c r="S18" s="42">
         <v>1.2</v>
       </c>
-      <c r="T18" s="46" t="str">
+      <c r="T18" s="42" t="str">
         <f>IFERROR(IF(ROUND(R18*1.2,1)=0,"",ROUND(R18*1.2,1)),"")</f>
         <v/>
       </c>
-      <c r="U18" s="46">
+      <c r="U18" s="42">
         <v>1.2</v>
       </c>
-      <c r="V18" s="46" t="str">
+      <c r="V18" s="42" t="str">
         <f>IFERROR(IF(ROUND(T18*1.2,1)=0,"",ROUND(T18*1.2,1)),"")</f>
         <v/>
       </c>
-      <c r="W18" s="46">
+      <c r="W18" s="42">
         <v>1.2</v>
       </c>
-      <c r="X18" s="46"/>
-      <c r="Y18" s="39" t="s">
+      <c r="X18" s="42"/>
+      <c r="Y18" s="35" t="s">
         <v>396</v>
       </c>
-      <c r="Z18" s="39" t="s">
+      <c r="Z18" s="35" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="19" spans="1:26" s="28" customFormat="1">
       <c r="A19" s="7"/>
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="35" t="s">
         <v>406</v>
       </c>
-      <c r="C19" s="39" t="s">
+      <c r="C19" s="35" t="s">
         <v>411</v>
       </c>
-      <c r="D19" s="39">
+      <c r="D19" s="35">
         <v>6</v>
       </c>
-      <c r="E19" s="39" t="s">
+      <c r="E19" s="35" t="s">
         <v>415</v>
       </c>
       <c r="F19" s="28" t="s">
@@ -7044,7 +7048,7 @@
       <c r="K19" s="28">
         <v>0</v>
       </c>
-      <c r="L19" s="39" t="s">
+      <c r="L19" s="35" t="s">
         <v>488</v>
       </c>
       <c r="M19" s="28">
@@ -7053,55 +7057,55 @@
       <c r="N19" s="28">
         <v>1</v>
       </c>
-      <c r="O19" s="46">
-        <v>1</v>
-      </c>
-      <c r="P19" s="46">
+      <c r="O19" s="42">
+        <v>1</v>
+      </c>
+      <c r="P19" s="42">
         <v>0.4</v>
       </c>
-      <c r="Q19" s="46">
-        <v>1</v>
-      </c>
-      <c r="R19" s="46">
+      <c r="Q19" s="42">
+        <v>1</v>
+      </c>
+      <c r="R19" s="42">
         <v>0.4</v>
       </c>
-      <c r="S19" s="46">
-        <v>1</v>
-      </c>
-      <c r="T19" s="46">
+      <c r="S19" s="42">
+        <v>1</v>
+      </c>
+      <c r="T19" s="42">
         <v>0.4</v>
       </c>
-      <c r="U19" s="46">
-        <v>1</v>
-      </c>
-      <c r="V19" s="46">
+      <c r="U19" s="42">
+        <v>1</v>
+      </c>
+      <c r="V19" s="42">
         <v>0.4</v>
       </c>
-      <c r="W19" s="46">
-        <v>1</v>
-      </c>
-      <c r="X19" s="46">
+      <c r="W19" s="42">
+        <v>1</v>
+      </c>
+      <c r="X19" s="42">
         <v>0.4</v>
       </c>
-      <c r="Y19" s="39" t="s">
+      <c r="Y19" s="35" t="s">
         <v>398</v>
       </c>
-      <c r="Z19" s="39" t="s">
+      <c r="Z19" s="35" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="20" spans="1:26" s="28" customFormat="1">
       <c r="A20" s="7"/>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="35" t="s">
         <v>408</v>
       </c>
-      <c r="C20" s="39" t="s">
+      <c r="C20" s="35" t="s">
         <v>411</v>
       </c>
-      <c r="D20" s="39">
+      <c r="D20" s="35">
         <v>7</v>
       </c>
-      <c r="E20" s="39" t="s">
+      <c r="E20" s="35" t="s">
         <v>417</v>
       </c>
       <c r="F20" s="28" t="s">
@@ -7125,117 +7129,117 @@
       <c r="L20" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="O20" s="46">
+      <c r="O20" s="42">
         <v>0.7</v>
       </c>
-      <c r="P20" s="46"/>
-      <c r="Q20" s="46">
+      <c r="P20" s="42"/>
+      <c r="Q20" s="42">
         <v>0.7</v>
       </c>
-      <c r="R20" s="46"/>
-      <c r="S20" s="46">
+      <c r="R20" s="42"/>
+      <c r="S20" s="42">
         <v>0.7</v>
       </c>
-      <c r="T20" s="46"/>
-      <c r="U20" s="46">
+      <c r="T20" s="42"/>
+      <c r="U20" s="42">
         <v>0.7</v>
       </c>
-      <c r="V20" s="46"/>
-      <c r="W20" s="46">
+      <c r="V20" s="42"/>
+      <c r="W20" s="42">
         <v>0.7</v>
       </c>
-      <c r="X20" s="46"/>
-      <c r="Y20" s="39" t="s">
+      <c r="X20" s="42"/>
+      <c r="Y20" s="35" t="s">
         <v>400</v>
       </c>
-      <c r="Z20" s="39" t="s">
+      <c r="Z20" s="35" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="21" spans="1:26" s="28" customFormat="1">
       <c r="A21" s="7"/>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="35" t="s">
         <v>410</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="35" t="s">
         <v>411</v>
       </c>
-      <c r="D21" s="39">
+      <c r="D21" s="35">
         <v>8</v>
       </c>
-      <c r="E21" s="39" t="s">
+      <c r="E21" s="35" t="s">
         <v>419</v>
       </c>
-      <c r="F21" s="39" t="s">
+      <c r="F21" s="35" t="s">
         <v>422</v>
       </c>
-      <c r="G21" s="39">
-        <v>0</v>
-      </c>
-      <c r="H21" s="39">
-        <v>0</v>
-      </c>
-      <c r="I21" s="39">
-        <v>1</v>
-      </c>
-      <c r="J21" s="39">
-        <v>1</v>
-      </c>
-      <c r="K21" s="39">
+      <c r="G21" s="35">
+        <v>0</v>
+      </c>
+      <c r="H21" s="35">
+        <v>0</v>
+      </c>
+      <c r="I21" s="35">
+        <v>1</v>
+      </c>
+      <c r="J21" s="35">
+        <v>1</v>
+      </c>
+      <c r="K21" s="35">
         <v>2</v>
       </c>
-      <c r="L21" s="39"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="39"/>
-      <c r="O21" s="46">
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="42">
         <v>0.7</v>
       </c>
-      <c r="P21" s="46">
+      <c r="P21" s="42">
         <v>0.05</v>
       </c>
-      <c r="Q21" s="46">
+      <c r="Q21" s="42">
         <v>0.7</v>
       </c>
-      <c r="R21" s="46">
+      <c r="R21" s="42">
         <v>0.05</v>
       </c>
-      <c r="S21" s="46">
+      <c r="S21" s="42">
         <v>0.7</v>
       </c>
-      <c r="T21" s="46">
+      <c r="T21" s="42">
         <v>0.05</v>
       </c>
-      <c r="U21" s="46">
+      <c r="U21" s="42">
         <v>0.7</v>
       </c>
-      <c r="V21" s="46">
+      <c r="V21" s="42">
         <v>0.05</v>
       </c>
-      <c r="W21" s="46">
+      <c r="W21" s="42">
         <v>0.7</v>
       </c>
-      <c r="X21" s="46">
+      <c r="X21" s="42">
         <v>0.05</v>
       </c>
-      <c r="Y21" s="39" t="s">
+      <c r="Y21" s="35" t="s">
         <v>402</v>
       </c>
-      <c r="Z21" s="39" t="s">
+      <c r="Z21" s="35" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="22" spans="1:26" s="28" customFormat="1">
       <c r="A22" s="7"/>
-      <c r="B22" s="39" t="s">
+      <c r="B22" s="35" t="s">
         <v>427</v>
       </c>
-      <c r="C22" s="39" t="s">
+      <c r="C22" s="35" t="s">
         <v>442</v>
       </c>
-      <c r="D22" s="39">
-        <v>1</v>
-      </c>
-      <c r="E22" s="39" t="s">
+      <c r="D22" s="35">
+        <v>1</v>
+      </c>
+      <c r="E22" s="35" t="s">
         <v>446</v>
       </c>
       <c r="F22" s="28" t="s">
@@ -7256,46 +7260,46 @@
       <c r="K22" s="28">
         <v>0</v>
       </c>
-      <c r="O22" s="46">
-        <v>1</v>
-      </c>
-      <c r="P22" s="46"/>
-      <c r="Q22" s="46">
-        <v>1</v>
-      </c>
-      <c r="R22" s="46"/>
-      <c r="S22" s="46">
-        <v>1</v>
-      </c>
-      <c r="T22" s="46"/>
-      <c r="U22" s="46">
-        <v>1</v>
-      </c>
-      <c r="V22" s="46"/>
-      <c r="W22" s="46">
-        <v>1</v>
-      </c>
-      <c r="X22" s="46"/>
-      <c r="Y22" s="39"/>
-      <c r="Z22" s="39" t="s">
+      <c r="O22" s="42">
+        <v>1</v>
+      </c>
+      <c r="P22" s="42"/>
+      <c r="Q22" s="42">
+        <v>1</v>
+      </c>
+      <c r="R22" s="42"/>
+      <c r="S22" s="42">
+        <v>1</v>
+      </c>
+      <c r="T22" s="42"/>
+      <c r="U22" s="42">
+        <v>1</v>
+      </c>
+      <c r="V22" s="42"/>
+      <c r="W22" s="42">
+        <v>1</v>
+      </c>
+      <c r="X22" s="42"/>
+      <c r="Y22" s="35"/>
+      <c r="Z22" s="35" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="23" spans="1:26" s="28" customFormat="1">
       <c r="A23" s="7"/>
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="35" t="s">
         <v>429</v>
       </c>
-      <c r="C23" s="39" t="s">
+      <c r="C23" s="35" t="s">
         <v>442</v>
       </c>
-      <c r="D23" s="39">
+      <c r="D23" s="35">
         <v>2</v>
       </c>
-      <c r="E23" s="39" t="s">
+      <c r="E23" s="35" t="s">
         <v>447</v>
       </c>
-      <c r="F23" s="39" t="s">
+      <c r="F23" s="35" t="s">
         <v>454</v>
       </c>
       <c r="G23" s="28">
@@ -7313,53 +7317,53 @@
       <c r="K23" s="28">
         <v>0</v>
       </c>
-      <c r="O23" s="46">
-        <v>1</v>
-      </c>
-      <c r="P23" s="46">
+      <c r="O23" s="42">
+        <v>1</v>
+      </c>
+      <c r="P23" s="42">
         <v>0.2</v>
       </c>
-      <c r="Q23" s="46">
-        <v>1</v>
-      </c>
-      <c r="R23" s="46">
+      <c r="Q23" s="42">
+        <v>1</v>
+      </c>
+      <c r="R23" s="42">
         <v>0.2</v>
       </c>
-      <c r="S23" s="46">
-        <v>1</v>
-      </c>
-      <c r="T23" s="46">
+      <c r="S23" s="42">
+        <v>1</v>
+      </c>
+      <c r="T23" s="42">
         <v>0.2</v>
       </c>
-      <c r="U23" s="46">
-        <v>1</v>
-      </c>
-      <c r="V23" s="46">
+      <c r="U23" s="42">
+        <v>1</v>
+      </c>
+      <c r="V23" s="42">
         <v>0.2</v>
       </c>
-      <c r="W23" s="46">
-        <v>1</v>
-      </c>
-      <c r="X23" s="46">
+      <c r="W23" s="42">
+        <v>1</v>
+      </c>
+      <c r="X23" s="42">
         <v>0.2</v>
       </c>
-      <c r="Y23" s="39"/>
-      <c r="Z23" s="39" t="s">
+      <c r="Y23" s="35"/>
+      <c r="Z23" s="35" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="24" spans="1:26" s="28" customFormat="1">
       <c r="A24" s="7"/>
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="35" t="s">
         <v>431</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="35" t="s">
         <v>442</v>
       </c>
-      <c r="D24" s="39">
+      <c r="D24" s="35">
         <v>3</v>
       </c>
-      <c r="E24" s="39" t="s">
+      <c r="E24" s="35" t="s">
         <v>448</v>
       </c>
       <c r="F24" s="28" t="s">
@@ -7386,56 +7390,56 @@
       <c r="M24" s="28">
         <v>0</v>
       </c>
-      <c r="O24" s="46">
+      <c r="O24" s="42">
         <v>0.7</v>
       </c>
-      <c r="P24" s="46">
+      <c r="P24" s="42">
         <v>0.7</v>
       </c>
-      <c r="Q24" s="46">
+      <c r="Q24" s="42">
         <v>0.7</v>
       </c>
-      <c r="R24" s="46">
+      <c r="R24" s="42">
         <v>0.7</v>
       </c>
-      <c r="S24" s="46">
+      <c r="S24" s="42">
         <v>0.7</v>
       </c>
-      <c r="T24" s="46">
+      <c r="T24" s="42">
         <v>0.7</v>
       </c>
-      <c r="U24" s="46">
+      <c r="U24" s="42">
         <v>0.7</v>
       </c>
-      <c r="V24" s="46">
+      <c r="V24" s="42">
         <v>0.7</v>
       </c>
-      <c r="W24" s="46">
+      <c r="W24" s="42">
         <v>0.7</v>
       </c>
-      <c r="X24" s="46">
+      <c r="X24" s="42">
         <v>0.7</v>
       </c>
-      <c r="Y24" s="39"/>
-      <c r="Z24" s="39" t="s">
+      <c r="Y24" s="35"/>
+      <c r="Z24" s="35" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="25" spans="1:26" s="28" customFormat="1">
       <c r="A25" s="7"/>
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="35" t="s">
         <v>433</v>
       </c>
-      <c r="C25" s="39" t="s">
+      <c r="C25" s="35" t="s">
         <v>442</v>
       </c>
-      <c r="D25" s="39">
+      <c r="D25" s="35">
         <v>4</v>
       </c>
-      <c r="E25" s="39" t="s">
+      <c r="E25" s="35" t="s">
         <v>449</v>
       </c>
-      <c r="F25" s="39" t="s">
+      <c r="F25" s="35" t="s">
         <v>455</v>
       </c>
       <c r="G25" s="28">
@@ -7453,53 +7457,53 @@
       <c r="K25" s="28">
         <v>0</v>
       </c>
-      <c r="O25" s="46">
-        <v>1</v>
-      </c>
-      <c r="P25" s="46">
+      <c r="O25" s="42">
+        <v>1</v>
+      </c>
+      <c r="P25" s="42">
         <v>0.1</v>
       </c>
-      <c r="Q25" s="46">
-        <v>1</v>
-      </c>
-      <c r="R25" s="46">
+      <c r="Q25" s="42">
+        <v>1</v>
+      </c>
+      <c r="R25" s="42">
         <v>0.1</v>
       </c>
-      <c r="S25" s="46">
-        <v>1</v>
-      </c>
-      <c r="T25" s="46">
+      <c r="S25" s="42">
+        <v>1</v>
+      </c>
+      <c r="T25" s="42">
         <v>0.1</v>
       </c>
-      <c r="U25" s="46">
-        <v>1</v>
-      </c>
-      <c r="V25" s="46">
+      <c r="U25" s="42">
+        <v>1</v>
+      </c>
+      <c r="V25" s="42">
         <v>0.1</v>
       </c>
-      <c r="W25" s="46">
-        <v>1</v>
-      </c>
-      <c r="X25" s="46">
+      <c r="W25" s="42">
+        <v>1</v>
+      </c>
+      <c r="X25" s="42">
         <v>0.1</v>
       </c>
-      <c r="Y25" s="39"/>
-      <c r="Z25" s="39" t="s">
+      <c r="Y25" s="35"/>
+      <c r="Z25" s="35" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="26" spans="1:26" s="28" customFormat="1">
       <c r="A26" s="7"/>
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="35" t="s">
         <v>435</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="35" t="s">
         <v>442</v>
       </c>
-      <c r="D26" s="39">
+      <c r="D26" s="35">
         <v>5</v>
       </c>
-      <c r="E26" s="39" t="s">
+      <c r="E26" s="35" t="s">
         <v>450</v>
       </c>
       <c r="F26" s="28" t="s">
@@ -7520,48 +7524,48 @@
       <c r="K26" s="28">
         <v>0</v>
       </c>
-      <c r="O26" s="46">
+      <c r="O26" s="42">
         <v>1.2</v>
       </c>
-      <c r="P26" s="46"/>
-      <c r="Q26" s="46">
+      <c r="P26" s="42"/>
+      <c r="Q26" s="42">
         <v>1.2</v>
       </c>
-      <c r="R26" s="46"/>
-      <c r="S26" s="46">
+      <c r="R26" s="42"/>
+      <c r="S26" s="42">
         <v>1.2</v>
       </c>
-      <c r="T26" s="46"/>
-      <c r="U26" s="46">
+      <c r="T26" s="42"/>
+      <c r="U26" s="42">
         <v>1.2</v>
       </c>
-      <c r="V26" s="46"/>
-      <c r="W26" s="46">
+      <c r="V26" s="42"/>
+      <c r="W26" s="42">
         <v>1.2</v>
       </c>
-      <c r="X26" s="46"/>
-      <c r="Y26" s="39" t="s">
+      <c r="X26" s="42"/>
+      <c r="Y26" s="35" t="s">
         <v>427</v>
       </c>
-      <c r="Z26" s="39" t="s">
+      <c r="Z26" s="35" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="27" spans="1:26" s="28" customFormat="1">
       <c r="A27" s="7"/>
-      <c r="B27" s="39" t="s">
+      <c r="B27" s="35" t="s">
         <v>437</v>
       </c>
-      <c r="C27" s="39" t="s">
+      <c r="C27" s="35" t="s">
         <v>442</v>
       </c>
-      <c r="D27" s="39">
+      <c r="D27" s="35">
         <v>6</v>
       </c>
-      <c r="E27" s="39" t="s">
+      <c r="E27" s="35" t="s">
         <v>451</v>
       </c>
-      <c r="F27" s="39" t="s">
+      <c r="F27" s="35" t="s">
         <v>454</v>
       </c>
       <c r="G27" s="28">
@@ -7579,55 +7583,55 @@
       <c r="K27" s="28">
         <v>0</v>
       </c>
-      <c r="O27" s="46">
+      <c r="O27" s="42">
         <v>1.2</v>
       </c>
-      <c r="P27" s="46">
+      <c r="P27" s="42">
         <v>0.3</v>
       </c>
-      <c r="Q27" s="46">
+      <c r="Q27" s="42">
         <v>1.2</v>
       </c>
-      <c r="R27" s="46">
+      <c r="R27" s="42">
         <v>0.3</v>
       </c>
-      <c r="S27" s="46">
+      <c r="S27" s="42">
         <v>1.2</v>
       </c>
-      <c r="T27" s="46">
+      <c r="T27" s="42">
         <v>0.3</v>
       </c>
-      <c r="U27" s="46">
+      <c r="U27" s="42">
         <v>1.2</v>
       </c>
-      <c r="V27" s="46">
+      <c r="V27" s="42">
         <v>0.3</v>
       </c>
-      <c r="W27" s="46">
+      <c r="W27" s="42">
         <v>1.2</v>
       </c>
-      <c r="X27" s="46">
+      <c r="X27" s="42">
         <v>0.3</v>
       </c>
-      <c r="Y27" s="39" t="s">
+      <c r="Y27" s="35" t="s">
         <v>429</v>
       </c>
-      <c r="Z27" s="39" t="s">
+      <c r="Z27" s="35" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="28" spans="1:26" s="28" customFormat="1">
       <c r="A28" s="7"/>
-      <c r="B28" s="39" t="s">
+      <c r="B28" s="35" t="s">
         <v>439</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="35" t="s">
         <v>442</v>
       </c>
-      <c r="D28" s="39">
+      <c r="D28" s="35">
         <v>7</v>
       </c>
-      <c r="E28" s="39" t="s">
+      <c r="E28" s="35" t="s">
         <v>452</v>
       </c>
       <c r="F28" s="28" t="s">
@@ -7654,58 +7658,58 @@
       <c r="M28" s="28">
         <v>0</v>
       </c>
-      <c r="O28" s="46">
+      <c r="O28" s="42">
         <v>0.9</v>
       </c>
-      <c r="P28" s="46">
+      <c r="P28" s="42">
         <v>0.9</v>
       </c>
-      <c r="Q28" s="46">
+      <c r="Q28" s="42">
         <v>0.9</v>
       </c>
-      <c r="R28" s="46">
+      <c r="R28" s="42">
         <v>0.9</v>
       </c>
-      <c r="S28" s="46">
+      <c r="S28" s="42">
         <v>0.9</v>
       </c>
-      <c r="T28" s="46">
+      <c r="T28" s="42">
         <v>0.9</v>
       </c>
-      <c r="U28" s="46">
+      <c r="U28" s="42">
         <v>0.9</v>
       </c>
-      <c r="V28" s="46">
+      <c r="V28" s="42">
         <v>0.9</v>
       </c>
-      <c r="W28" s="46">
+      <c r="W28" s="42">
         <v>0.9</v>
       </c>
-      <c r="X28" s="46">
+      <c r="X28" s="42">
         <v>0.9</v>
       </c>
-      <c r="Y28" s="39" t="s">
+      <c r="Y28" s="35" t="s">
         <v>431</v>
       </c>
-      <c r="Z28" s="39" t="s">
+      <c r="Z28" s="35" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="29" spans="1:26" s="28" customFormat="1">
       <c r="A29" s="7"/>
-      <c r="B29" s="39" t="s">
+      <c r="B29" s="35" t="s">
         <v>441</v>
       </c>
-      <c r="C29" s="39" t="s">
+      <c r="C29" s="35" t="s">
         <v>442</v>
       </c>
-      <c r="D29" s="39">
+      <c r="D29" s="35">
         <v>8</v>
       </c>
-      <c r="E29" s="39" t="s">
+      <c r="E29" s="35" t="s">
         <v>453</v>
       </c>
-      <c r="F29" s="39" t="s">
+      <c r="F29" s="35" t="s">
         <v>455</v>
       </c>
       <c r="G29" s="28">
@@ -7723,580 +7727,580 @@
       <c r="K29" s="28">
         <v>0</v>
       </c>
-      <c r="O29" s="46">
+      <c r="O29" s="42">
         <v>1.2</v>
       </c>
-      <c r="P29" s="46">
+      <c r="P29" s="42">
         <v>0.15</v>
       </c>
-      <c r="Q29" s="46">
+      <c r="Q29" s="42">
         <v>1.2</v>
       </c>
-      <c r="R29" s="46">
+      <c r="R29" s="42">
         <v>0.15</v>
       </c>
-      <c r="S29" s="46">
+      <c r="S29" s="42">
         <v>1.2</v>
       </c>
-      <c r="T29" s="46">
+      <c r="T29" s="42">
         <v>0.15</v>
       </c>
-      <c r="U29" s="46">
+      <c r="U29" s="42">
         <v>1.2</v>
       </c>
-      <c r="V29" s="46">
+      <c r="V29" s="42">
         <v>0.15</v>
       </c>
-      <c r="W29" s="46">
+      <c r="W29" s="42">
         <v>1.2</v>
       </c>
-      <c r="X29" s="46">
+      <c r="X29" s="42">
         <v>0.15</v>
       </c>
-      <c r="Y29" s="39" t="s">
+      <c r="Y29" s="35" t="s">
         <v>433</v>
       </c>
-      <c r="Z29" s="39" t="s">
+      <c r="Z29" s="35" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="30" spans="1:26" s="28" customFormat="1">
       <c r="A30" s="7"/>
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="35" t="s">
         <v>457</v>
       </c>
-      <c r="C30" s="39" t="s">
+      <c r="C30" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D30" s="39">
-        <v>1</v>
-      </c>
-      <c r="E30" s="39" t="s">
+      <c r="D30" s="35">
+        <v>1</v>
+      </c>
+      <c r="E30" s="35" t="s">
         <v>476</v>
       </c>
-      <c r="F30" s="39" t="s">
+      <c r="F30" s="35" t="s">
         <v>484</v>
       </c>
-      <c r="G30" s="39">
-        <v>0</v>
-      </c>
-      <c r="H30" s="39">
-        <v>1</v>
-      </c>
-      <c r="I30" s="39">
-        <v>1</v>
-      </c>
-      <c r="J30" s="39">
-        <v>1</v>
-      </c>
-      <c r="K30" s="39">
-        <v>0</v>
-      </c>
-      <c r="L30" s="39"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="46">
+      <c r="G30" s="35">
+        <v>0</v>
+      </c>
+      <c r="H30" s="35">
+        <v>1</v>
+      </c>
+      <c r="I30" s="35">
+        <v>1</v>
+      </c>
+      <c r="J30" s="35">
+        <v>1</v>
+      </c>
+      <c r="K30" s="35">
+        <v>0</v>
+      </c>
+      <c r="L30" s="35"/>
+      <c r="M30" s="35"/>
+      <c r="N30" s="35"/>
+      <c r="O30" s="42">
         <v>0.5</v>
       </c>
-      <c r="P30" s="46"/>
-      <c r="Q30" s="46">
+      <c r="P30" s="42"/>
+      <c r="Q30" s="42">
         <v>0.5</v>
       </c>
-      <c r="R30" s="46"/>
-      <c r="S30" s="46">
+      <c r="R30" s="42"/>
+      <c r="S30" s="42">
         <v>0.5</v>
       </c>
-      <c r="T30" s="46"/>
-      <c r="U30" s="46">
+      <c r="T30" s="42"/>
+      <c r="U30" s="42">
         <v>0.5</v>
       </c>
-      <c r="V30" s="46"/>
-      <c r="W30" s="46">
+      <c r="V30" s="42"/>
+      <c r="W30" s="42">
         <v>0.5</v>
       </c>
-      <c r="X30" s="46"/>
-      <c r="Y30" s="39"/>
-      <c r="Z30" s="39" t="s">
+      <c r="X30" s="42"/>
+      <c r="Y30" s="35"/>
+      <c r="Z30" s="35" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="31" spans="1:26" s="28" customFormat="1">
       <c r="A31" s="7"/>
-      <c r="B31" s="39" t="s">
+      <c r="B31" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D31" s="39">
+      <c r="D31" s="35">
         <v>2</v>
       </c>
-      <c r="E31" s="39" t="s">
+      <c r="E31" s="35" t="s">
         <v>477</v>
       </c>
-      <c r="F31" s="39" t="s">
+      <c r="F31" s="35" t="s">
         <v>485</v>
       </c>
-      <c r="G31" s="39">
-        <v>0</v>
-      </c>
-      <c r="H31" s="39">
-        <v>0</v>
-      </c>
-      <c r="I31" s="39">
-        <v>1</v>
-      </c>
-      <c r="J31" s="39">
-        <v>1</v>
-      </c>
-      <c r="K31" s="39">
-        <v>0</v>
-      </c>
-      <c r="L31" s="39"/>
-      <c r="M31" s="39"/>
-      <c r="N31" s="39"/>
-      <c r="O31" s="46">
+      <c r="G31" s="35">
+        <v>0</v>
+      </c>
+      <c r="H31" s="35">
+        <v>0</v>
+      </c>
+      <c r="I31" s="35">
+        <v>1</v>
+      </c>
+      <c r="J31" s="35">
+        <v>1</v>
+      </c>
+      <c r="K31" s="35">
+        <v>0</v>
+      </c>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="42">
         <v>0.8</v>
       </c>
-      <c r="P31" s="46"/>
-      <c r="Q31" s="46">
+      <c r="P31" s="42"/>
+      <c r="Q31" s="42">
         <v>0.8</v>
       </c>
-      <c r="R31" s="46"/>
-      <c r="S31" s="46">
+      <c r="R31" s="42"/>
+      <c r="S31" s="42">
         <v>0.8</v>
       </c>
-      <c r="T31" s="46"/>
-      <c r="U31" s="46">
+      <c r="T31" s="42"/>
+      <c r="U31" s="42">
         <v>0.8</v>
       </c>
-      <c r="V31" s="46"/>
-      <c r="W31" s="46">
+      <c r="V31" s="42"/>
+      <c r="W31" s="42">
         <v>0.8</v>
       </c>
-      <c r="X31" s="46"/>
-      <c r="Y31" s="39"/>
-      <c r="Z31" s="39" t="s">
+      <c r="X31" s="42"/>
+      <c r="Y31" s="35"/>
+      <c r="Z31" s="35" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="32" spans="1:26" s="28" customFormat="1">
       <c r="A32" s="7"/>
-      <c r="B32" s="39" t="s">
+      <c r="B32" s="35" t="s">
         <v>461</v>
       </c>
-      <c r="C32" s="39" t="s">
+      <c r="C32" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D32" s="39">
+      <c r="D32" s="35">
         <v>3</v>
       </c>
-      <c r="E32" s="39" t="s">
+      <c r="E32" s="35" t="s">
         <v>478</v>
       </c>
-      <c r="F32" s="39" t="s">
+      <c r="F32" s="35" t="s">
         <v>486</v>
       </c>
-      <c r="G32" s="39">
-        <v>0</v>
-      </c>
-      <c r="H32" s="39">
-        <v>1</v>
-      </c>
-      <c r="I32" s="39">
-        <v>1</v>
-      </c>
-      <c r="J32" s="39">
-        <v>1</v>
-      </c>
-      <c r="K32" s="39">
-        <v>1</v>
-      </c>
-      <c r="L32" s="39" t="s">
+      <c r="G32" s="35">
+        <v>0</v>
+      </c>
+      <c r="H32" s="35">
+        <v>1</v>
+      </c>
+      <c r="I32" s="35">
+        <v>1</v>
+      </c>
+      <c r="J32" s="35">
+        <v>1</v>
+      </c>
+      <c r="K32" s="35">
+        <v>1</v>
+      </c>
+      <c r="L32" s="35" t="s">
         <v>488</v>
       </c>
-      <c r="M32" s="39">
-        <v>1</v>
-      </c>
-      <c r="N32" s="39">
-        <v>1</v>
-      </c>
-      <c r="O32" s="46">
+      <c r="M32" s="35">
+        <v>1</v>
+      </c>
+      <c r="N32" s="35">
+        <v>1</v>
+      </c>
+      <c r="O32" s="42">
         <v>0.3</v>
       </c>
-      <c r="P32" s="46">
+      <c r="P32" s="42">
         <v>0.3</v>
       </c>
-      <c r="Q32" s="46">
+      <c r="Q32" s="42">
         <v>0.3</v>
       </c>
-      <c r="R32" s="46">
+      <c r="R32" s="42">
         <v>0.3</v>
       </c>
-      <c r="S32" s="46">
+      <c r="S32" s="42">
         <v>0.3</v>
       </c>
-      <c r="T32" s="46">
+      <c r="T32" s="42">
         <v>0.3</v>
       </c>
-      <c r="U32" s="46">
+      <c r="U32" s="42">
         <v>0.3</v>
       </c>
-      <c r="V32" s="46">
+      <c r="V32" s="42">
         <v>0.3</v>
       </c>
-      <c r="W32" s="46">
+      <c r="W32" s="42">
         <v>0.3</v>
       </c>
-      <c r="X32" s="46">
+      <c r="X32" s="42">
         <v>0.3</v>
       </c>
-      <c r="Y32" s="39"/>
-      <c r="Z32" s="39" t="s">
+      <c r="Y32" s="35"/>
+      <c r="Z32" s="35" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="33" spans="1:26" s="28" customFormat="1">
       <c r="A33" s="7"/>
-      <c r="B33" s="39" t="s">
+      <c r="B33" s="35" t="s">
         <v>463</v>
       </c>
-      <c r="C33" s="39" t="s">
+      <c r="C33" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D33" s="39">
+      <c r="D33" s="35">
         <v>4</v>
       </c>
-      <c r="E33" s="39" t="s">
+      <c r="E33" s="35" t="s">
         <v>479</v>
       </c>
-      <c r="F33" s="47" t="s">
+      <c r="F33" s="43" t="s">
         <v>487</v>
       </c>
-      <c r="G33" s="39">
-        <v>0</v>
-      </c>
-      <c r="H33" s="39">
+      <c r="G33" s="35">
+        <v>0</v>
+      </c>
+      <c r="H33" s="35">
         <v>2</v>
       </c>
-      <c r="I33" s="39">
-        <v>1</v>
-      </c>
-      <c r="J33" s="39">
-        <v>1</v>
-      </c>
-      <c r="K33" s="39">
+      <c r="I33" s="35">
+        <v>1</v>
+      </c>
+      <c r="J33" s="35">
+        <v>1</v>
+      </c>
+      <c r="K33" s="35">
         <v>2</v>
       </c>
-      <c r="L33" s="39"/>
-      <c r="M33" s="39"/>
-      <c r="N33" s="39"/>
-      <c r="O33" s="46">
+      <c r="L33" s="35"/>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
+      <c r="O33" s="42">
         <v>0.2</v>
       </c>
-      <c r="P33" s="46">
+      <c r="P33" s="42">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="46">
+      <c r="Q33" s="42">
         <v>0.2</v>
       </c>
-      <c r="R33" s="46">
+      <c r="R33" s="42">
         <v>0.2</v>
       </c>
-      <c r="S33" s="46">
+      <c r="S33" s="42">
         <v>0.2</v>
       </c>
-      <c r="T33" s="46">
+      <c r="T33" s="42">
         <v>0.2</v>
       </c>
-      <c r="U33" s="46">
+      <c r="U33" s="42">
         <v>0.2</v>
       </c>
-      <c r="V33" s="46">
+      <c r="V33" s="42">
         <v>0.2</v>
       </c>
-      <c r="W33" s="46">
+      <c r="W33" s="42">
         <v>0.2</v>
       </c>
-      <c r="X33" s="46">
+      <c r="X33" s="42">
         <v>0.2</v>
       </c>
-      <c r="Y33" s="39"/>
-      <c r="Z33" s="39" t="s">
+      <c r="Y33" s="35"/>
+      <c r="Z33" s="35" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="34" spans="1:26" s="28" customFormat="1">
       <c r="A34" s="7"/>
-      <c r="B34" s="39" t="s">
+      <c r="B34" s="35" t="s">
         <v>465</v>
       </c>
-      <c r="C34" s="39" t="s">
+      <c r="C34" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D34" s="39">
+      <c r="D34" s="35">
         <v>5</v>
       </c>
-      <c r="E34" s="39" t="s">
+      <c r="E34" s="35" t="s">
         <v>480</v>
       </c>
-      <c r="F34" s="39" t="s">
+      <c r="F34" s="35" t="s">
         <v>484</v>
       </c>
-      <c r="G34" s="39">
-        <v>0</v>
-      </c>
-      <c r="H34" s="39">
-        <v>1</v>
-      </c>
-      <c r="I34" s="39">
-        <v>1</v>
-      </c>
-      <c r="J34" s="39">
-        <v>1</v>
-      </c>
-      <c r="K34" s="39">
-        <v>0</v>
-      </c>
-      <c r="L34" s="39"/>
-      <c r="M34" s="39"/>
-      <c r="N34" s="39"/>
-      <c r="O34" s="46">
+      <c r="G34" s="35">
+        <v>0</v>
+      </c>
+      <c r="H34" s="35">
+        <v>1</v>
+      </c>
+      <c r="I34" s="35">
+        <v>1</v>
+      </c>
+      <c r="J34" s="35">
+        <v>1</v>
+      </c>
+      <c r="K34" s="35">
+        <v>0</v>
+      </c>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
+      <c r="N34" s="35"/>
+      <c r="O34" s="42">
         <v>0.7</v>
       </c>
-      <c r="P34" s="46"/>
-      <c r="Q34" s="46">
+      <c r="P34" s="42"/>
+      <c r="Q34" s="42">
         <v>0.7</v>
       </c>
-      <c r="R34" s="46"/>
-      <c r="S34" s="46">
+      <c r="R34" s="42"/>
+      <c r="S34" s="42">
         <v>0.7</v>
       </c>
-      <c r="T34" s="46"/>
-      <c r="U34" s="46">
+      <c r="T34" s="42"/>
+      <c r="U34" s="42">
         <v>0.7</v>
       </c>
-      <c r="V34" s="46"/>
-      <c r="W34" s="46">
+      <c r="V34" s="42"/>
+      <c r="W34" s="42">
         <v>0.7</v>
       </c>
-      <c r="X34" s="46"/>
-      <c r="Y34" s="39" t="s">
+      <c r="X34" s="42"/>
+      <c r="Y34" s="35" t="s">
         <v>457</v>
       </c>
-      <c r="Z34" s="39" t="s">
+      <c r="Z34" s="35" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="35" spans="1:26" s="28" customFormat="1">
       <c r="A35" s="7"/>
-      <c r="B35" s="39" t="s">
+      <c r="B35" s="35" t="s">
         <v>467</v>
       </c>
-      <c r="C35" s="39" t="s">
+      <c r="C35" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D35" s="39">
+      <c r="D35" s="35">
         <v>6</v>
       </c>
-      <c r="E35" s="39" t="s">
+      <c r="E35" s="35" t="s">
         <v>481</v>
       </c>
-      <c r="F35" s="39" t="s">
+      <c r="F35" s="35" t="s">
         <v>485</v>
       </c>
-      <c r="G35" s="39">
-        <v>0</v>
-      </c>
-      <c r="H35" s="39">
-        <v>0</v>
-      </c>
-      <c r="I35" s="39">
-        <v>1</v>
-      </c>
-      <c r="J35" s="39">
-        <v>1</v>
-      </c>
-      <c r="K35" s="39">
-        <v>0</v>
-      </c>
-      <c r="L35" s="39"/>
-      <c r="M35" s="39"/>
-      <c r="N35" s="39"/>
-      <c r="O35" s="46">
-        <v>1</v>
-      </c>
-      <c r="P35" s="46"/>
-      <c r="Q35" s="46">
-        <v>1</v>
-      </c>
-      <c r="R35" s="46"/>
-      <c r="S35" s="46">
-        <v>1</v>
-      </c>
-      <c r="T35" s="46"/>
-      <c r="U35" s="46">
-        <v>1</v>
-      </c>
-      <c r="V35" s="46"/>
-      <c r="W35" s="46">
-        <v>1</v>
-      </c>
-      <c r="X35" s="46"/>
-      <c r="Y35" s="39" t="s">
+      <c r="G35" s="35">
+        <v>0</v>
+      </c>
+      <c r="H35" s="35">
+        <v>0</v>
+      </c>
+      <c r="I35" s="35">
+        <v>1</v>
+      </c>
+      <c r="J35" s="35">
+        <v>1</v>
+      </c>
+      <c r="K35" s="35">
+        <v>0</v>
+      </c>
+      <c r="L35" s="35"/>
+      <c r="M35" s="35"/>
+      <c r="N35" s="35"/>
+      <c r="O35" s="42">
+        <v>1</v>
+      </c>
+      <c r="P35" s="42"/>
+      <c r="Q35" s="42">
+        <v>1</v>
+      </c>
+      <c r="R35" s="42"/>
+      <c r="S35" s="42">
+        <v>1</v>
+      </c>
+      <c r="T35" s="42"/>
+      <c r="U35" s="42">
+        <v>1</v>
+      </c>
+      <c r="V35" s="42"/>
+      <c r="W35" s="42">
+        <v>1</v>
+      </c>
+      <c r="X35" s="42"/>
+      <c r="Y35" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="Z35" s="39" t="s">
+      <c r="Z35" s="35" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="36" spans="1:26" s="28" customFormat="1">
       <c r="A36" s="7"/>
-      <c r="B36" s="39" t="s">
+      <c r="B36" s="35" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="39" t="s">
+      <c r="C36" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D36" s="39">
+      <c r="D36" s="35">
         <v>7</v>
       </c>
-      <c r="E36" s="39" t="s">
+      <c r="E36" s="35" t="s">
         <v>482</v>
       </c>
-      <c r="F36" s="39" t="s">
+      <c r="F36" s="35" t="s">
         <v>486</v>
       </c>
-      <c r="G36" s="39">
-        <v>0</v>
-      </c>
-      <c r="H36" s="39">
-        <v>1</v>
-      </c>
-      <c r="I36" s="39">
-        <v>1</v>
-      </c>
-      <c r="J36" s="39">
-        <v>1</v>
-      </c>
-      <c r="K36" s="39">
-        <v>1</v>
-      </c>
-      <c r="L36" s="39" t="s">
+      <c r="G36" s="35">
+        <v>0</v>
+      </c>
+      <c r="H36" s="35">
+        <v>1</v>
+      </c>
+      <c r="I36" s="35">
+        <v>1</v>
+      </c>
+      <c r="J36" s="35">
+        <v>1</v>
+      </c>
+      <c r="K36" s="35">
+        <v>1</v>
+      </c>
+      <c r="L36" s="35" t="s">
         <v>488</v>
       </c>
-      <c r="M36" s="39">
-        <v>1</v>
-      </c>
-      <c r="N36" s="39">
-        <v>1</v>
-      </c>
-      <c r="O36" s="46">
+      <c r="M36" s="35">
+        <v>1</v>
+      </c>
+      <c r="N36" s="35">
+        <v>1</v>
+      </c>
+      <c r="O36" s="42">
         <v>0.5</v>
       </c>
-      <c r="P36" s="46">
+      <c r="P36" s="42">
         <v>0.5</v>
       </c>
-      <c r="Q36" s="46">
+      <c r="Q36" s="42">
         <v>0.5</v>
       </c>
-      <c r="R36" s="46">
+      <c r="R36" s="42">
         <v>0.5</v>
       </c>
-      <c r="S36" s="46">
+      <c r="S36" s="42">
         <v>0.5</v>
       </c>
-      <c r="T36" s="46">
+      <c r="T36" s="42">
         <v>0.5</v>
       </c>
-      <c r="U36" s="46">
+      <c r="U36" s="42">
         <v>0.5</v>
       </c>
-      <c r="V36" s="46">
+      <c r="V36" s="42">
         <v>0.5</v>
       </c>
-      <c r="W36" s="46">
+      <c r="W36" s="42">
         <v>0.5</v>
       </c>
-      <c r="X36" s="46">
+      <c r="X36" s="42">
         <v>0.5</v>
       </c>
-      <c r="Y36" s="39" t="s">
+      <c r="Y36" s="35" t="s">
         <v>461</v>
       </c>
-      <c r="Z36" s="39" t="s">
+      <c r="Z36" s="35" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="37" spans="1:26" s="28" customFormat="1">
       <c r="A37" s="7"/>
-      <c r="B37" s="39" t="s">
+      <c r="B37" s="35" t="s">
         <v>471</v>
       </c>
-      <c r="C37" s="39" t="s">
+      <c r="C37" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D37" s="39">
+      <c r="D37" s="35">
         <v>8</v>
       </c>
-      <c r="E37" s="39" t="s">
+      <c r="E37" s="35" t="s">
         <v>483</v>
       </c>
-      <c r="F37" s="47" t="s">
+      <c r="F37" s="43" t="s">
         <v>487</v>
       </c>
-      <c r="G37" s="39">
-        <v>0</v>
-      </c>
-      <c r="H37" s="39">
+      <c r="G37" s="35">
+        <v>0</v>
+      </c>
+      <c r="H37" s="35">
         <v>2</v>
       </c>
-      <c r="I37" s="39">
-        <v>1</v>
-      </c>
-      <c r="J37" s="39">
-        <v>1</v>
-      </c>
-      <c r="K37" s="39">
+      <c r="I37" s="35">
+        <v>1</v>
+      </c>
+      <c r="J37" s="35">
+        <v>1</v>
+      </c>
+      <c r="K37" s="35">
         <v>2</v>
       </c>
-      <c r="L37" s="39"/>
-      <c r="M37" s="39"/>
-      <c r="N37" s="39"/>
-      <c r="O37" s="46">
+      <c r="L37" s="35"/>
+      <c r="M37" s="35"/>
+      <c r="N37" s="35"/>
+      <c r="O37" s="42">
         <v>0.3</v>
       </c>
-      <c r="P37" s="46">
+      <c r="P37" s="42">
         <v>0.3</v>
       </c>
-      <c r="Q37" s="46">
+      <c r="Q37" s="42">
         <v>0.3</v>
       </c>
-      <c r="R37" s="46">
+      <c r="R37" s="42">
         <v>0.3</v>
       </c>
-      <c r="S37" s="46">
+      <c r="S37" s="42">
         <v>0.3</v>
       </c>
-      <c r="T37" s="46">
+      <c r="T37" s="42">
         <v>0.3</v>
       </c>
-      <c r="U37" s="46">
+      <c r="U37" s="42">
         <v>0.3</v>
       </c>
-      <c r="V37" s="46">
+      <c r="V37" s="42">
         <v>0.3</v>
       </c>
-      <c r="W37" s="46">
+      <c r="W37" s="42">
         <v>0.3</v>
       </c>
-      <c r="X37" s="46">
+      <c r="X37" s="42">
         <v>0.3</v>
       </c>
-      <c r="Y37" s="39" t="s">
+      <c r="Y37" s="35" t="s">
         <v>463</v>
       </c>
-      <c r="Z37" s="39" t="s">
+      <c r="Z37" s="35" t="s">
         <v>472</v>
       </c>
     </row>
@@ -8392,30 +8396,30 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{047AFDEF-8474-49A1-AB6C-5E66602F6994}">
   <dimension ref="A1:AR13"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="10.5" style="11" customWidth="1"/>
-    <col min="2" max="3" width="20.5625" style="11" customWidth="1"/>
+    <col min="2" max="3" width="20.58203125" style="11" customWidth="1"/>
     <col min="4" max="4" width="36" style="11" customWidth="1"/>
-    <col min="5" max="24" width="20.5625" style="11" customWidth="1"/>
-    <col min="25" max="25" width="24.1875" style="11" customWidth="1"/>
+    <col min="5" max="24" width="20.58203125" style="11" customWidth="1"/>
+    <col min="25" max="25" width="24.1640625" style="11" customWidth="1"/>
     <col min="26" max="26" width="44.5" style="11" customWidth="1"/>
-    <col min="27" max="27" width="20.5625" style="11" customWidth="1"/>
-    <col min="28" max="28" width="19.6875" style="11" customWidth="1"/>
-    <col min="29" max="31" width="20.5625" style="11" customWidth="1"/>
-    <col min="32" max="32" width="22.9375" style="11" customWidth="1"/>
-    <col min="33" max="33" width="20.5625" style="11" customWidth="1"/>
+    <col min="27" max="27" width="20.58203125" style="11" customWidth="1"/>
+    <col min="28" max="28" width="19.6640625" style="11" customWidth="1"/>
+    <col min="29" max="31" width="20.58203125" style="11" customWidth="1"/>
+    <col min="32" max="32" width="22.9140625" style="11" customWidth="1"/>
+    <col min="33" max="33" width="20.58203125" style="11" customWidth="1"/>
     <col min="34" max="34" width="26.25" style="11" customWidth="1"/>
-    <col min="35" max="35" width="20.5625" style="11" customWidth="1"/>
-    <col min="36" max="36" width="25.4375" style="11" customWidth="1"/>
-    <col min="37" max="37" width="20.5625" style="11" customWidth="1"/>
+    <col min="35" max="35" width="20.58203125" style="11" customWidth="1"/>
+    <col min="36" max="36" width="25.4140625" style="11" customWidth="1"/>
+    <col min="37" max="37" width="20.58203125" style="11" customWidth="1"/>
     <col min="38" max="38" width="25" style="11" customWidth="1"/>
-    <col min="39" max="39" width="20.5625" style="11" customWidth="1"/>
-    <col min="40" max="40" width="24.5625" style="11" customWidth="1"/>
-    <col min="41" max="41" width="20.5625" style="11" customWidth="1"/>
-    <col min="42" max="42" width="24.5625" style="11" customWidth="1"/>
-    <col min="43" max="43" width="20.5625" style="11" customWidth="1"/>
-    <col min="44" max="44" width="24.5625" style="11" customWidth="1"/>
+    <col min="39" max="39" width="20.58203125" style="11" customWidth="1"/>
+    <col min="40" max="40" width="24.58203125" style="11" customWidth="1"/>
+    <col min="41" max="41" width="20.58203125" style="11" customWidth="1"/>
+    <col min="42" max="42" width="24.58203125" style="11" customWidth="1"/>
+    <col min="43" max="43" width="20.58203125" style="11" customWidth="1"/>
+    <col min="44" max="44" width="24.58203125" style="11" customWidth="1"/>
     <col min="45" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
@@ -8425,35 +8429,35 @@
       </c>
     </row>
     <row r="2" spans="1:44">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="46" t="s">
         <v>216</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="47"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="47"/>
     </row>
     <row r="4" spans="1:44">
       <c r="A4" s="11" t="s">
         <v>182</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>19</v>
@@ -8582,7 +8586,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="5" spans="1:44" ht="33.75">
+    <row r="5" spans="1:44" ht="34">
       <c r="A5" s="11" t="s">
         <v>184</v>
       </c>
@@ -8716,500 +8720,500 @@
         <v>245</v>
       </c>
     </row>
-    <row r="6" spans="1:44" ht="50.65">
+    <row r="6" spans="1:44" ht="51">
       <c r="A6" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="34" t="s">
         <v>308</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="34" t="s">
         <v>298</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="38" t="s">
         <v>303</v>
       </c>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38">
-        <v>1</v>
-      </c>
-      <c r="K6" s="38">
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34">
+        <v>1</v>
+      </c>
+      <c r="K6" s="34">
         <v>2</v>
       </c>
-      <c r="L6" s="38">
+      <c r="L6" s="34">
         <v>3</v>
       </c>
-      <c r="M6" s="38">
+      <c r="M6" s="34">
         <v>4</v>
       </c>
-      <c r="N6" s="38">
+      <c r="N6" s="34">
         <v>5</v>
       </c>
-      <c r="O6" s="38"/>
-      <c r="P6" s="38"/>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="38"/>
-      <c r="S6" s="38"/>
-      <c r="T6" s="38"/>
-      <c r="U6" s="38"/>
-      <c r="V6" s="38"/>
-      <c r="W6" s="38"/>
-      <c r="X6" s="38" t="s">
+      <c r="O6" s="34"/>
+      <c r="P6" s="34"/>
+      <c r="Q6" s="34"/>
+      <c r="R6" s="34"/>
+      <c r="S6" s="34"/>
+      <c r="T6" s="34"/>
+      <c r="U6" s="34"/>
+      <c r="V6" s="34"/>
+      <c r="W6" s="34"/>
+      <c r="X6" s="34" t="s">
         <v>313</v>
       </c>
-      <c r="Y6" s="38" t="s">
+      <c r="Y6" s="34" t="s">
         <v>318</v>
       </c>
-      <c r="Z6" s="42" t="s">
+      <c r="Z6" s="38" t="s">
         <v>323</v>
       </c>
-      <c r="AA6" s="42">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="38">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="38">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="38">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="38">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="38"/>
-      <c r="AG6" s="38"/>
-      <c r="AH6" s="38"/>
-      <c r="AI6" s="43">
+      <c r="AA6" s="38">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="34">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="34">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="34">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="34">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="34"/>
+      <c r="AG6" s="34"/>
+      <c r="AH6" s="34"/>
+      <c r="AI6" s="39">
         <v>0.8</v>
       </c>
-      <c r="AJ6" s="43"/>
-      <c r="AK6" s="43">
+      <c r="AJ6" s="39"/>
+      <c r="AK6" s="39">
         <v>0.9</v>
       </c>
-      <c r="AL6" s="43" t="str">
+      <c r="AL6" s="39" t="str">
         <f t="shared" ref="AL6:AR10" si="0">IFERROR(IF(ROUND(AJ6*1.2,1)=0,"",ROUND(AJ6*1.2,1)),"")</f>
         <v/>
       </c>
-      <c r="AM6" s="43">
-        <v>1</v>
-      </c>
-      <c r="AN6" s="43" t="str">
+      <c r="AM6" s="39">
+        <v>1</v>
+      </c>
+      <c r="AN6" s="39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO6" s="43">
+      <c r="AO6" s="39">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AP6" s="43" t="str">
+      <c r="AP6" s="39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AQ6" s="43">
+      <c r="AQ6" s="39">
         <v>1.2</v>
       </c>
-      <c r="AR6" s="43" t="str">
+      <c r="AR6" s="39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:44" ht="33.75">
-      <c r="B7" s="38" t="s">
+    <row r="7" spans="1:44" ht="34">
+      <c r="B7" s="34" t="s">
         <v>309</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="34" t="s">
         <v>299</v>
       </c>
-      <c r="D7" s="42" t="s">
+      <c r="D7" s="38" t="s">
         <v>304</v>
       </c>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38">
-        <v>1</v>
-      </c>
-      <c r="K7" s="38">
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34">
+        <v>1</v>
+      </c>
+      <c r="K7" s="34">
         <v>2</v>
       </c>
-      <c r="L7" s="38">
+      <c r="L7" s="34">
         <v>3</v>
       </c>
-      <c r="M7" s="38">
+      <c r="M7" s="34">
         <v>4</v>
       </c>
-      <c r="N7" s="38">
+      <c r="N7" s="34">
         <v>5</v>
       </c>
-      <c r="O7" s="38"/>
-      <c r="P7" s="38"/>
-      <c r="Q7" s="38"/>
-      <c r="R7" s="38"/>
-      <c r="S7" s="38"/>
-      <c r="T7" s="38"/>
-      <c r="U7" s="38"/>
-      <c r="V7" s="38"/>
-      <c r="W7" s="38"/>
-      <c r="X7" s="38" t="s">
+      <c r="O7" s="34"/>
+      <c r="P7" s="34"/>
+      <c r="Q7" s="34"/>
+      <c r="R7" s="34"/>
+      <c r="S7" s="34"/>
+      <c r="T7" s="34"/>
+      <c r="U7" s="34"/>
+      <c r="V7" s="34"/>
+      <c r="W7" s="34"/>
+      <c r="X7" s="34" t="s">
         <v>314</v>
       </c>
-      <c r="Y7" s="38" t="s">
+      <c r="Y7" s="34" t="s">
         <v>319</v>
       </c>
-      <c r="Z7" s="42" t="s">
+      <c r="Z7" s="38" t="s">
         <v>324</v>
       </c>
-      <c r="AA7" s="42">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="38">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="38">
-        <v>1</v>
-      </c>
-      <c r="AD7" s="38">
-        <v>1</v>
-      </c>
-      <c r="AE7" s="38">
+      <c r="AA7" s="38">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="34">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="34">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="34">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="34">
         <v>2</v>
       </c>
-      <c r="AF7" s="38"/>
-      <c r="AG7" s="38"/>
-      <c r="AH7" s="38"/>
-      <c r="AI7" s="43">
+      <c r="AF7" s="34"/>
+      <c r="AG7" s="34"/>
+      <c r="AH7" s="34"/>
+      <c r="AI7" s="39">
         <v>0.3</v>
       </c>
-      <c r="AJ7" s="43"/>
-      <c r="AK7" s="43">
+      <c r="AJ7" s="39"/>
+      <c r="AK7" s="39">
         <v>0.4</v>
       </c>
-      <c r="AL7" s="43" t="str">
+      <c r="AL7" s="39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM7" s="43">
+      <c r="AM7" s="39">
         <v>0.5</v>
       </c>
-      <c r="AN7" s="43" t="str">
+      <c r="AN7" s="39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO7" s="43">
+      <c r="AO7" s="39">
         <v>0.6</v>
       </c>
-      <c r="AP7" s="43" t="str">
+      <c r="AP7" s="39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AQ7" s="43">
+      <c r="AQ7" s="39">
         <v>0.7</v>
       </c>
-      <c r="AR7" s="43" t="str">
+      <c r="AR7" s="39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:44" ht="50.65">
-      <c r="B8" s="38" t="s">
+    <row r="8" spans="1:44" ht="51">
+      <c r="B8" s="34" t="s">
         <v>310</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="34" t="s">
         <v>300</v>
       </c>
-      <c r="D8" s="42" t="s">
+      <c r="D8" s="38" t="s">
         <v>305</v>
       </c>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="38">
-        <v>1</v>
-      </c>
-      <c r="P8" s="38">
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="34">
+        <v>1</v>
+      </c>
+      <c r="P8" s="34">
         <v>2</v>
       </c>
-      <c r="Q8" s="38">
+      <c r="Q8" s="34">
         <v>3</v>
       </c>
-      <c r="R8" s="38">
+      <c r="R8" s="34">
         <v>4</v>
       </c>
-      <c r="S8" s="38">
+      <c r="S8" s="34">
         <v>5</v>
       </c>
-      <c r="T8" s="38"/>
-      <c r="U8" s="38"/>
-      <c r="V8" s="38"/>
-      <c r="W8" s="38"/>
-      <c r="X8" s="38" t="s">
+      <c r="T8" s="34"/>
+      <c r="U8" s="34"/>
+      <c r="V8" s="34"/>
+      <c r="W8" s="34"/>
+      <c r="X8" s="34" t="s">
         <v>315</v>
       </c>
-      <c r="Y8" s="38" t="s">
+      <c r="Y8" s="34" t="s">
         <v>320</v>
       </c>
-      <c r="Z8" s="42" t="s">
+      <c r="Z8" s="38" t="s">
         <v>325</v>
       </c>
-      <c r="AA8" s="42">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="42">
+      <c r="AA8" s="38">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="38">
         <v>3</v>
       </c>
-      <c r="AC8" s="42">
-        <v>1</v>
-      </c>
-      <c r="AD8" s="42">
-        <v>1</v>
-      </c>
-      <c r="AE8" s="42">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="42"/>
-      <c r="AG8" s="42"/>
-      <c r="AH8" s="42"/>
-      <c r="AI8" s="44">
+      <c r="AC8" s="38">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="38">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="38">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="38"/>
+      <c r="AG8" s="38"/>
+      <c r="AH8" s="38"/>
+      <c r="AI8" s="40">
         <v>0.3</v>
       </c>
-      <c r="AJ8" s="44"/>
-      <c r="AK8" s="43">
+      <c r="AJ8" s="40"/>
+      <c r="AK8" s="39">
         <v>0.35</v>
       </c>
-      <c r="AL8" s="43" t="str">
+      <c r="AL8" s="39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM8" s="43">
+      <c r="AM8" s="39">
         <v>0.4</v>
       </c>
-      <c r="AN8" s="43" t="str">
+      <c r="AN8" s="39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO8" s="43">
+      <c r="AO8" s="39">
         <v>0.45</v>
       </c>
-      <c r="AP8" s="43" t="str">
+      <c r="AP8" s="39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AQ8" s="43">
+      <c r="AQ8" s="39">
         <v>0.5</v>
       </c>
-      <c r="AR8" s="43" t="str">
+      <c r="AR8" s="39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:44" ht="33.75">
-      <c r="B9" s="38" t="s">
+    <row r="9" spans="1:44" ht="34">
+      <c r="B9" s="34" t="s">
         <v>311</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="34" t="s">
         <v>301</v>
       </c>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="38" t="s">
         <v>306</v>
       </c>
-      <c r="E9" s="38">
-        <v>1</v>
-      </c>
-      <c r="F9" s="38">
+      <c r="E9" s="34">
+        <v>1</v>
+      </c>
+      <c r="F9" s="34">
         <v>2</v>
       </c>
-      <c r="G9" s="38">
+      <c r="G9" s="34">
         <v>3</v>
       </c>
-      <c r="H9" s="38">
+      <c r="H9" s="34">
         <v>4</v>
       </c>
-      <c r="I9" s="38">
+      <c r="I9" s="34">
         <v>5</v>
       </c>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="38"/>
-      <c r="N9" s="38"/>
-      <c r="O9" s="38"/>
-      <c r="P9" s="38"/>
-      <c r="Q9" s="38"/>
-      <c r="R9" s="38"/>
-      <c r="S9" s="38"/>
-      <c r="T9" s="38"/>
-      <c r="U9" s="38"/>
-      <c r="V9" s="38"/>
-      <c r="W9" s="38"/>
-      <c r="X9" s="38" t="s">
+      <c r="J9" s="34"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="34"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="34"/>
+      <c r="P9" s="34"/>
+      <c r="Q9" s="34"/>
+      <c r="R9" s="34"/>
+      <c r="S9" s="34"/>
+      <c r="T9" s="34"/>
+      <c r="U9" s="34"/>
+      <c r="V9" s="34"/>
+      <c r="W9" s="34"/>
+      <c r="X9" s="34" t="s">
         <v>316</v>
       </c>
-      <c r="Y9" s="38" t="s">
+      <c r="Y9" s="34" t="s">
         <v>321</v>
       </c>
-      <c r="Z9" s="42" t="s">
+      <c r="Z9" s="38" t="s">
         <v>326</v>
       </c>
-      <c r="AA9" s="42">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="42">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="42">
-        <v>1</v>
-      </c>
-      <c r="AD9" s="42">
-        <v>1</v>
-      </c>
-      <c r="AE9" s="42">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="42"/>
-      <c r="AG9" s="42"/>
-      <c r="AH9" s="42"/>
-      <c r="AI9" s="44">
+      <c r="AA9" s="38">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="38">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="38">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="38">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="38">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="38"/>
+      <c r="AG9" s="38"/>
+      <c r="AH9" s="38"/>
+      <c r="AI9" s="40">
         <v>0.3</v>
       </c>
-      <c r="AJ9" s="44"/>
-      <c r="AK9" s="43">
+      <c r="AJ9" s="40"/>
+      <c r="AK9" s="39">
         <v>0.35</v>
       </c>
-      <c r="AL9" s="43" t="str">
+      <c r="AL9" s="39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM9" s="43">
+      <c r="AM9" s="39">
         <v>0.4</v>
       </c>
-      <c r="AN9" s="43" t="str">
+      <c r="AN9" s="39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO9" s="43">
+      <c r="AO9" s="39">
         <v>0.45</v>
       </c>
-      <c r="AP9" s="43" t="str">
+      <c r="AP9" s="39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AQ9" s="43">
+      <c r="AQ9" s="39">
         <v>0.5</v>
       </c>
-      <c r="AR9" s="43" t="str">
+      <c r="AR9" s="39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:44" ht="33.75">
-      <c r="B10" s="38" t="s">
+    <row r="10" spans="1:44" ht="34">
+      <c r="B10" s="34" t="s">
         <v>312</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="34" t="s">
         <v>302</v>
       </c>
-      <c r="D10" s="42" t="s">
+      <c r="D10" s="38" t="s">
         <v>307</v>
       </c>
-      <c r="E10" s="38">
-        <v>1</v>
-      </c>
-      <c r="F10" s="38">
+      <c r="E10" s="34">
+        <v>1</v>
+      </c>
+      <c r="F10" s="34">
         <v>2</v>
       </c>
-      <c r="G10" s="38">
+      <c r="G10" s="34">
         <v>3</v>
       </c>
-      <c r="H10" s="38">
+      <c r="H10" s="34">
         <v>4</v>
       </c>
-      <c r="I10" s="38">
+      <c r="I10" s="34">
         <v>5</v>
       </c>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="38"/>
-      <c r="O10" s="38"/>
-      <c r="P10" s="38"/>
-      <c r="Q10" s="38"/>
-      <c r="R10" s="38"/>
-      <c r="S10" s="38"/>
-      <c r="T10" s="38"/>
-      <c r="U10" s="38"/>
-      <c r="V10" s="38"/>
-      <c r="W10" s="38"/>
-      <c r="X10" s="38" t="s">
+      <c r="J10" s="34"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="34"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="34"/>
+      <c r="P10" s="34"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="34"/>
+      <c r="S10" s="34"/>
+      <c r="T10" s="34"/>
+      <c r="U10" s="34"/>
+      <c r="V10" s="34"/>
+      <c r="W10" s="34"/>
+      <c r="X10" s="34" t="s">
         <v>317</v>
       </c>
-      <c r="Y10" s="38" t="s">
+      <c r="Y10" s="34" t="s">
         <v>322</v>
       </c>
-      <c r="Z10" s="42" t="s">
+      <c r="Z10" s="38" t="s">
         <v>327</v>
       </c>
-      <c r="AA10" s="42">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="38">
+      <c r="AA10" s="38">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="34">
         <v>4</v>
       </c>
-      <c r="AC10" s="38">
-        <v>1</v>
-      </c>
-      <c r="AD10" s="38">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="38">
+      <c r="AC10" s="34">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="34">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="34">
         <v>2</v>
       </c>
-      <c r="AF10" s="38"/>
-      <c r="AG10" s="38"/>
-      <c r="AH10" s="38"/>
-      <c r="AI10" s="43">
+      <c r="AF10" s="34"/>
+      <c r="AG10" s="34"/>
+      <c r="AH10" s="34"/>
+      <c r="AI10" s="39">
         <v>0.1</v>
       </c>
-      <c r="AJ10" s="43"/>
-      <c r="AK10" s="43">
+      <c r="AJ10" s="39"/>
+      <c r="AK10" s="39">
         <v>0.15</v>
       </c>
-      <c r="AL10" s="43" t="str">
+      <c r="AL10" s="39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM10" s="43">
+      <c r="AM10" s="39">
         <v>0.2</v>
       </c>
-      <c r="AN10" s="43" t="str">
+      <c r="AN10" s="39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO10" s="43">
+      <c r="AO10" s="39">
         <v>0.25</v>
       </c>
-      <c r="AP10" s="43" t="str">
+      <c r="AP10" s="39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AQ10" s="43">
+      <c r="AQ10" s="39">
         <v>0.3</v>
       </c>
-      <c r="AR10" s="43" t="str">
+      <c r="AR10" s="39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -9219,7 +9223,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="13" spans="1:44" ht="101.25">
+    <row r="13" spans="1:44" ht="102">
       <c r="A13" s="11" t="s">
         <v>181</v>
       </c>
@@ -9366,141 +9370,141 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB342C4C-71E0-4A34-A845-61B8600DB9F8}">
   <dimension ref="B3:D14"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="3" max="3" width="11.4375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.4140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="63.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:4">
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="36" t="s">
         <v>353</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="36" t="s">
         <v>361</v>
       </c>
-      <c r="D3" s="45" t="s">
+      <c r="D3" s="41" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="33.75">
-      <c r="B4" s="40" t="s">
+    <row r="4" spans="2:4" ht="34">
+      <c r="B4" s="36" t="s">
         <v>354</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="36" t="s">
         <v>363</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="37" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="5" spans="2:4">
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="36" t="s">
         <v>355</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="36" t="s">
         <v>365</v>
       </c>
-      <c r="D5" s="45" t="s">
+      <c r="D5" s="41" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="6" spans="2:4">
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="36" t="s">
         <v>367</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="36" t="s">
         <v>368</v>
       </c>
-      <c r="D6" s="41" t="s">
+      <c r="D6" s="37" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="7" spans="2:4">
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="36" t="s">
         <v>370</v>
       </c>
-      <c r="C7" s="40" t="s">
+      <c r="C7" s="36" t="s">
         <v>371</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="37" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="8" spans="2:4">
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="36" t="s">
         <v>373</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="36" t="s">
         <v>374</v>
       </c>
-      <c r="D8" s="41" t="s">
+      <c r="D8" s="37" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="9" spans="2:4">
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="36" t="s">
         <v>375</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="36" t="s">
         <v>376</v>
       </c>
-      <c r="D9" s="45" t="s">
+      <c r="D9" s="41" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="10" spans="2:4">
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="36" t="s">
         <v>378</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="36" t="s">
         <v>379</v>
       </c>
-      <c r="D10" s="41" t="s">
+      <c r="D10" s="37" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="11" spans="2:4">
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="36" t="s">
         <v>380</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="36" t="s">
         <v>381</v>
       </c>
-      <c r="D11" s="45" t="s">
+      <c r="D11" s="41" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="12" spans="2:4">
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="36" t="s">
         <v>385</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="36" t="s">
         <v>386</v>
       </c>
-      <c r="D12" s="41" t="s">
+      <c r="D12" s="37" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="13" spans="2:4">
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="36" t="s">
         <v>387</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="36" t="s">
         <v>388</v>
       </c>
-      <c r="D13" s="45" t="s">
+      <c r="D13" s="41" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="14" spans="2:4">
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="36" t="s">
         <v>389</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="36" t="s">
         <v>390</v>
       </c>
-      <c r="D14" s="41" t="s">
+      <c r="D14" s="37" t="s">
         <v>391</v>
       </c>
     </row>

--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 알파 전투 밸런스 데이터 테이블 V2.0.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 알파 전투 밸런스 데이터 테이블 V2.0.xlsx
@@ -3,14 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HeroInfluencetmp\Assets\_ProtoType_Merge\ASB\Data\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDC38A7-4E31-48C2-A568-A43977B431A8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="834" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="834" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="수정 내역" sheetId="41" r:id="rId1"/>
@@ -24,532 +18,532 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" chartTrackingRefBase="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="549">
-  <si>
-    <t>Class</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CriticalRate</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Speed</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>스피드</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CounterRate</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>회피율</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>반격율</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>치명타율</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>레벨</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassSkillName</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>직업 스킬명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassSkillDescription</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>직업 스킬 설명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassSkillIndex</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>직업 스킬 인덱스</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponSkillIndex</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponName</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponSkillName</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnemyIndex</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponIndex</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>list&lt;int&gt;</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnitAI</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적군 유닛명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnemyName</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassName</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassConcept</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassIndex</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>직업명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WaeponDescription</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BonusSpeed</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BonusCriticalRate</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BonusCounterRate</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassSkillIndexList</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponIndexList</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ReduceRate</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적군 유닛
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="551">
+  <si>
+    <t xml:space="preserve">Class</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">CriticalRate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Speed</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">스피드</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">CounterRate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">회피율</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">반격율</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">치명타율</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">레벨</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassSkillName</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">직업 스킬명</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassSkillDescription</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">직업 스킬 설명</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassSkillIndex</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">직업 스킬 인덱스</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">WeaponSkillIndex</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">WeaponName</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">WeaponSkillName</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EnemyIndex</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">WeaponIndex</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">list&lt;int&gt;</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">UnitAI</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적군 유닛명</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EnemyName</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassName</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassConcept</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassIndex</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">직업명</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">WaeponDescription</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BonusSpeed</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BonusCriticalRate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BonusCounterRate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassSkillIndexList</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">WeaponIndexList</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ReduceRate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적군 유닛
 인덱스</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>EnemyConcept</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnemySkill1
+    <t xml:space="preserve">EnemyConcept</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EnemySkill1
 Name</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>EnemySkill1
+    <t xml:space="preserve">EnemySkill1
 Description</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>적군 스킬1
+    <t xml:space="preserve">적군 스킬1
 설명</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>적군 스킬2
+    <t xml:space="preserve">적군 스킬2
 설명</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>EnemySkill2
+    <t xml:space="preserve">EnemySkill2
 Name</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>EnemySkill2
+    <t xml:space="preserve">EnemySkill2
 Description</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>적군 유닛 행동 규칙</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적군 스킬1 스킬명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적군 스킬2 스킬명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponSkillDescription</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponSkillEffect</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponSkillRange</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponSkillTarget</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기 스킬 사정거리
+    <t xml:space="preserve">적군 유닛 행동 규칙</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적군 스킬1 스킬명</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적군 스킬2 스킬명</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">WeaponSkillDescription</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">WeaponSkillEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">WeaponSkillRange</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">WeaponSkillTarget</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무기 스킬 사정거리
 (0 근거리 1 원거리)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>무기 스킬 대상
+    <t xml:space="preserve">무기 스킬 대상
 (0 단일 1 복수 2 전체)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>직업 스킬 대상
+    <t xml:space="preserve">직업 스킬 대상
 (0 단일 1 복수 2 전체)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>직업 스킬 사정거리
+    <t xml:space="preserve">직업 스킬 사정거리
 (0 근거리 1 원거리)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>ClassSkillEffect</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassSkillRange</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassSkillTarget</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적군 스킬 1 사정거리
+    <t xml:space="preserve">ClassSkillEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassSkillRange</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassSkillTarget</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적군 스킬 1 사정거리
 (0 근거리 1 원거리)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>적군 스킬 1 대상
+    <t xml:space="preserve">적군 스킬 1 대상
 (0 단일 1 복수 2 전체)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>적군 스킬 2 대상
+    <t xml:space="preserve">적군 스킬 2 대상
 (0 단일 1 복수 2 전체)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>적군 스킬 2 계수</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적군 스킬 1 계수</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnemySkill1Effect</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnemySkill1Range</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnemySkill1Target</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnemySkill1Value</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnemySkill2Effect</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnemySkill2Range</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnemySkill2Target</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnemySkill2Value</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BonusReduceRate</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>경험치</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExperiencePoint</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassSkillMultiTarget</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassSkill
+    <t xml:space="preserve">적군 스킬 2 계수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적군 스킬 1 계수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EnemySkill1Effect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EnemySkill1Range</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EnemySkill1Target</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EnemySkill1Value</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EnemySkill2Effect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EnemySkill2Range</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EnemySkill2Target</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EnemySkill2Value</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BonusReduceRate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">경험치</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ExperiencePoint</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassSkillMultiTarget</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassSkill
 MultiTargetType</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>ClassSkill
+    <t xml:space="preserve">ClassSkill
 MultiTargetCount</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>직업 스킬 복수 대상
+    <t xml:space="preserve">직업 스킬 복수 대상
 (스킬 대상 1일 경우)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>직업 스킬 
+    <t xml:space="preserve">직업 스킬 
 복수 추가 대상 수
 (스킬 대상 1일 경우)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>{3}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>직업 스킬 
+    <t xml:space="preserve">{3}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">직업 스킬 
 복수 대상 타입
 (0 후보 전체 1 랜덤)
 (스킬 대상 1일 경우)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>WeaponSkillMultiTarget</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponSkill
+    <t xml:space="preserve">WeaponSkillMultiTarget</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">WeaponSkill
 MultiTargetType</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>무기 스킬 복수 대상
+    <t xml:space="preserve">무기 스킬 복수 대상
 (스킬 대상 1일 경우)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>무기 스킬 
+    <t xml:space="preserve">무기 스킬 
 복수 대상 타입
 (0 후보 전체 1 랜덤)
 (스킬 대상 1일 경우)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>무기 스킬 
+    <t xml:space="preserve">무기 스킬 
 복수 추가 대상 수
 (스킬 대상 1일 경우)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>EnemySkill1MultiTarget</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnemySkill1
+    <t xml:space="preserve">EnemySkill1MultiTarget</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EnemySkill1
 MultiTargetType</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>EnemySkill1
+    <t xml:space="preserve">EnemySkill1
 MultiTargetCount</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>EnemySkill2MultiTarget</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnemySkill2
+    <t xml:space="preserve">EnemySkill2MultiTarget</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EnemySkill2
 MultiTargetType</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>EnemySkill2
+    <t xml:space="preserve">EnemySkill2
 MultiTargetCount</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>적군 스킬 1 복수 대상
+    <t xml:space="preserve">적군 스킬 1 복수 대상
 (스킬 대상 1일 경우)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>적군 스킬 1
+    <t xml:space="preserve">적군 스킬 1
 복수 대상 타입
 (0 후보 전체 1 랜덤)
 (스킬 대상 1일 경우)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>적군 스킬 1
+    <t xml:space="preserve">적군 스킬 1
 복수 추가 대상 수
 (스킬 대상 1일 경우)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>적군 스킬 2 복수 대상
+    <t xml:space="preserve">적군 스킬 2 복수 대상
 (스킬 대상 1일 경우)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>적군 스킬 2
+    <t xml:space="preserve">적군 스킬 2
 복수 대상 타입
 (0 후보 전체 1 랜덤)
 (스킬 대상 1일 경우)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>적군 스킬 2
+    <t xml:space="preserve">적군 스킬 2
 복수 추가 대상 수
 (스킬 대상 1일 경우)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>유닛 체력</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>유닛 공격력</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>유닛 방어력</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>유닛당 랭크업
+    <t xml:space="preserve">유닛 체력</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">유닛 공격력</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">유닛 방어력</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">유닛당 랭크업
 필요 경험치</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>S</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>A</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>B</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>C</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>D</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>F</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>유닛 최대 체력</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnitDEF</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnitATK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnitMaxHP</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IPCost</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IP 코스트</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적군 스킬 2 사정거리
+    <t xml:space="preserve">S</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">B</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">F</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">유닛 최대 체력</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">UnitDEF</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">UnitATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">UnitMaxHP</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">IPCost</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">IP 코스트</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적군 스킬 2 사정거리
 (0 근거리 1 원거리)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>WeaponSkillRangeLine</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassSkillRangeLine</t>
+    <t xml:space="preserve">WeaponSkillRangeLine</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassSkillRangeLine</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -561,7 +555,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>무기 스킬
+    <t xml:space="preserve">무기 스킬
 사정거리 라인
 0 전열 우선 (적 전열이 있을 경우 전열 공격) 
 1 전열/후열 선택 가능 
@@ -569,15 +563,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>EnemySkill1RangeLine</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnemySkill2RangeLine</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적군 스킬 2
+    <t xml:space="preserve">EnemySkill1RangeLine</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EnemySkill2RangeLine</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적군 스킬 2
 사정거리 라인
 0 전열 우선 (전열이 있을 경우 전열 공격) 
 1 전열/후열 선택 가능
@@ -585,7 +579,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>적군 스킬 1
+    <t xml:space="preserve">적군 스킬 1
 사정거리 라인
 0 전열 우선 (전열이 있을 경우 전열 공격) 
 1 전열/후열 선택 가능
@@ -596,281 +590,281 @@
     <t xml:space="preserve">최대 I.P 추가 </t>
   </si>
   <si>
-    <t>블래스터</t>
-  </si>
-  <si>
-    <t>스트라이커</t>
-  </si>
-  <si>
-    <t>서포터</t>
-  </si>
-  <si>
-    <t>파이터</t>
-  </si>
-  <si>
-    <t>적군 스킬 2 효과
+    <t xml:space="preserve">블래스터</t>
+  </si>
+  <si>
+    <t xml:space="preserve">스트라이커</t>
+  </si>
+  <si>
+    <t xml:space="preserve">서포터</t>
+  </si>
+  <si>
+    <t xml:space="preserve">파이터</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적군 스킬 2 효과
 (0 공격 1 회복 2 부활)</t>
   </si>
   <si>
-    <t>직업 스킬 효과
+    <t xml:space="preserve">직업 스킬 효과
 (0 공격 1 회복 2 부활)</t>
   </si>
   <si>
-    <t>{9}</t>
-  </si>
-  <si>
-    <t>{0}</t>
-  </si>
-  <si>
-    <t>LevelGrowthMaxHP</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LevelGrowthMaxAtk</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LevelGrowthMaxDef</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기 스킬 계수 Lv1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponSkillValueLv1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponSkillSubValueLv1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기 스킬
+    <t xml:space="preserve">{9}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LevelGrowthMaxHP</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LevelGrowthMaxAtk</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LevelGrowthMaxDef</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무기 스킬 계수 Lv1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">WeaponSkillValueLv1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">WeaponSkillSubValueLv1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무기 스킬
 추가 계수 Lv1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>WeaponSkillValueLv2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기 스킬 계수 Lv2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponSkillSubValueLv2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기 스킬
+    <t xml:space="preserve">WeaponSkillValueLv2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무기 스킬 계수 Lv2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">WeaponSkillSubValueLv2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무기 스킬
 추가 계수 Lv2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>WeaponSkillSubValueLv3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponSkillValueLv3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기 스킬 계수 Lv3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기 스킬
+    <t xml:space="preserve">WeaponSkillSubValueLv3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">WeaponSkillValueLv3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무기 스킬 계수 Lv3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무기 스킬
 추가 계수 Lv3</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>BonusMaxHPLv1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BonusMaxHPLv2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BonusMaxHPLv3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BonusATKLv1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BonusATKLv2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BonusATKLv3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BonusDEFLv1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BonusDEFLv2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BonusDEFLv3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassSkillSubValueLv1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassSkillValueLv1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassSkillValueLv2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassSkillSubValueLv2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassSkillValueLv3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassSkillSubValueLv3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassSkillValueLv4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassSkillSubValueLv4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>직업 스킬 계수 Lv1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>직업 스킬 추가 계수 Lv1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>직업 스킬 계수 Lv2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>직업 스킬 추가 계수 Lv2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>직업 스킬 계수 Lv3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>직업 스킬 추가 계수 Lv3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>직업 스킬 계수 Lv4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>직업 스킬 추가 계수 Lv4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적 1명에게 {ClassSkillValue} 대미지를 입히고, 1턴 동안 해당 대상이 단일 공격 시 자신을 공격하게 한다. (적 전열이 있을 경우, 전열 우선 공격)</t>
-  </si>
-  <si>
-    <t>적 1명에게 {ClassSkillValue} 대미지를 입힌다.</t>
-  </si>
-  <si>
-    <t>적 1명에게 {ClassSkillValue} 대미지를 입힌다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>전열의 적 한 명에게 {ClassSkillValue} 대미지를 입히고, 해당 후열에 있는 적 한 명에게 추가로 {ClassSkillSubValue} 대미지를 입힌다. (전열의 적이 없을 경우 후열의 적 한 명만을 공격)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적 1명에게 {ClassSkillValue}대미지를 두 번 입힌다. (치명타, 회피율 판정은 각각 계산한다.)</t>
+    <t xml:space="preserve">BonusMaxHPLv1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BonusMaxHPLv2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BonusMaxHPLv3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BonusATKLv1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BonusATKLv2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BonusATKLv3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BonusDEFLv1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BonusDEFLv2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BonusDEFLv3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassSkillSubValueLv1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassSkillValueLv1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassSkillValueLv2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassSkillSubValueLv2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassSkillValueLv3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassSkillSubValueLv3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassSkillValueLv4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassSkillSubValueLv4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">직업 스킬 계수 Lv1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">직업 스킬 추가 계수 Lv1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">직업 스킬 계수 Lv2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">직업 스킬 추가 계수 Lv2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">직업 스킬 계수 Lv3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">직업 스킬 추가 계수 Lv3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">직업 스킬 계수 Lv4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">직업 스킬 추가 계수 Lv4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적 1명에게 {ClassSkillValue} 대미지를 입히고, 1턴 동안 해당 대상이 단일 공격 시 자신을 공격하게 한다. (적 전열이 있을 경우, 전열 우선 공격)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 1명에게 {ClassSkillValue} 대미지를 입힌다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 1명에게 {ClassSkillValue} 대미지를 입힌다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">전열의 적 한 명에게 {ClassSkillValue} 대미지를 입히고, 해당 후열에 있는 적 한 명에게 추가로 {ClassSkillSubValue} 대미지를 입힌다. (전열의 적이 없을 경우 후열의 적 한 명만을 공격)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적 1명에게 {ClassSkillValue}대미지를 두 번 입힌다. (치명타, 회피율 판정은 각각 계산한다.)</t>
   </si>
   <si>
     <t xml:space="preserve"> 습득 랭크</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>ClassSkill
+    <t xml:space="preserve">ClassSkill
 AcquireRank</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>UnitName</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>#Comment</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>#Type</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>percent</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>#Name</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>#Data</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>#End</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>여긴 안씀</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>아군 유닛 식별용 
+    <t xml:space="preserve">UnitName</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">#Comment</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">#Type</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">percent</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">#Name</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">#Data</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">#End</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">여긴 안씀</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">아군 유닛 식별용 
 인덱스</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>인게임상
+    <t xml:space="preserve">인게임상
 표기 클래스</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>인게임상
+    <t xml:space="preserve">인게임상
 표기 설명</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>유닛 크리티컬율</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>유닛 피해 경감율</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>유닛 반격률</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>유닛 스피드</t>
+    <t xml:space="preserve">유닛 크리티컬율</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">유닛 피해 경감율</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">유닛 반격률</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">유닛 스피드</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -878,540 +872,540 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>유닛 사용하는 무기 리스트</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>레벨당 증가 체력</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>레벨당 증가 공격력</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>레벨당 증가 방어력</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponSkillMultiTargetCount</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기 식별용 
+    <t xml:space="preserve">유닛 사용하는 무기 리스트</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">레벨당 증가 체력</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">레벨당 증가 공격력</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">레벨당 증가 방어력</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">WeaponSkillMultiTargetCount</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무기 식별용 
 인덱스</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>인게임상
+    <t xml:space="preserve">인게임상
 표기 장비 이름</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Lv1일 때
+    <t xml:space="preserve">Lv1일 때
 무기 체력</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Lv2일 때
+    <t xml:space="preserve">Lv2일 때
 무기 체력</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Lv3일 때
+    <t xml:space="preserve">Lv3일 때
 무기 체력</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Lv1일 때
+    <t xml:space="preserve">Lv1일 때
 무기 공격력</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Lv2일 때
+    <t xml:space="preserve">Lv2일 때
 무기 공격력</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Lv3일 때
+    <t xml:space="preserve">Lv3일 때
 무기 공격력</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Lv1일 때
+    <t xml:space="preserve">Lv1일 때
 무기 방어력</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Lv2일 때
+    <t xml:space="preserve">Lv2일 때
 무기 방어력</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Lv3일 때
+    <t xml:space="preserve">Lv3일 때
 무기 방어력</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>무기 치명타율</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기 반격률</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기 피해 경감율</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기 스피드</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기 데이터 테이블</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>아군 유닛 스테이터스 데이터 테이블</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기 스킬 인덱스용 테이블</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>인게임 표기 무기 스킬명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>인게임 표기 무기 설명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적군 유닛 테이블</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>인게임용 적군 유닛 콘셉트</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>아군 유닛 클래스별 직업 스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassSkillValueLv5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassSkillSubValueLv5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>직업 스킬 계수 Lv5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>직업 스킬 추가 계수 Lv5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BonusMaxHPLv4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BonusMaxHPLv5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lv4일 때
+    <t xml:space="preserve">무기 치명타율</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무기 반격률</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무기 피해 경감율</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무기 스피드</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무기 데이터 테이블</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">아군 유닛 스테이터스 데이터 테이블</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무기 스킬 인덱스용 테이블</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">인게임 표기 무기 스킬명</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">인게임 표기 무기 설명</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적군 유닛 테이블</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">인게임용 적군 유닛 콘셉트</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">아군 유닛 클래스별 직업 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassSkillValueLv5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassSkillSubValueLv5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">직업 스킬 계수 Lv5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">직업 스킬 추가 계수 Lv5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BonusMaxHPLv4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BonusMaxHPLv5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Lv4일 때
 무기 체력</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Lv5일 때
+    <t xml:space="preserve">Lv5일 때
 무기 체력</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>BonusATKLv4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lv4일 때
+    <t xml:space="preserve">BonusATKLv4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Lv4일 때
 무기 공격력</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>BonusATKLv5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lv5일 때
+    <t xml:space="preserve">BonusATKLv5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Lv5일 때
 무기 공격력</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>BonusDEFLv4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lv34 때
+    <t xml:space="preserve">BonusDEFLv4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Lv34 때
 무기 방어력</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>BonusDEFLv5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lv5일 때
+    <t xml:space="preserve">BonusDEFLv5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Lv5일 때
 무기 방어력</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>WeaponSkillValueLv4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponSkillSubValueLv4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기 스킬 계수 Lv4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기 스킬
+    <t xml:space="preserve">WeaponSkillValueLv4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">WeaponSkillSubValueLv4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무기 스킬 계수 Lv4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무기 스킬
 추가 계수 Lv4</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>WeaponSkillValueLv5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponSkillSubValueLv5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기 스킬 계수 Lv5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기 스킬
+    <t xml:space="preserve">WeaponSkillValueLv5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">WeaponSkillSubValueLv5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무기 스킬 계수 Lv5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무기 스킬
 추가 계수 Lv5</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>인게임 상 표기</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Level</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rank</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>NeedExpieriencePoint</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>AddIP</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>저스티스</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>평균적인 능력치를 지닌 근거리 히어로</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>루미나</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>다중 공격에 특화된 원거리 히어로</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>블랙 불릿</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>단일 공격에 특화된 원거리 히어로</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>네코밍</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>회복이 가능한 원거리 히어로</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>인게임상
+    <t xml:space="preserve">인게임 상 표기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Level</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">NeedExpieriencePoint</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">AddIP</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">저스티스</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">평균적인 능력치를 지닌 근거리 히어로</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">루미나</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">다중 공격에 특화된 원거리 히어로</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">블랙 불릿</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">단일 공격에 특화된 원거리 히어로</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">네코밍</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">회복이 가능한 원거리 히어로</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">인게임상
 표기 이름</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SS</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SSS</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적군 부대 테이블</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemy1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemy1Slot</t>
+    <t xml:space="preserve">SS</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SSS</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적군 부대 테이블</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Enemy1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Enemy1Slot</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Enemy2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemy2Slot</t>
+    <t xml:space="preserve">Enemy2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Enemy2Slot</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Enemy3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemy3Slot</t>
+    <t xml:space="preserve">Enemy3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Enemy3Slot</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Enemy4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemy4Slot</t>
+    <t xml:space="preserve">Enemy4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Enemy4Slot</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Enemy5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemy5Slot</t>
+    <t xml:space="preserve">Enemy5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Enemy5Slot</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>유닛 위치</t>
+    <t xml:space="preserve">유닛 위치</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>하급 2</t>
+    <t xml:space="preserve">하급 2</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>하급 3</t>
+    <t xml:space="preserve">하급 3</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>하급 2+중급1</t>
+    <t xml:space="preserve">하급 2+중급1</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>하급 2+중급2</t>
+    <t xml:space="preserve">하급 2+중급2</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>하급2+중급2+상급1</t>
+    <t xml:space="preserve">하급2+중급2+상급1</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>하급</t>
+    <t xml:space="preserve">하급</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>중급</t>
+    <t xml:space="preserve">중급</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>상급</t>
+    <t xml:space="preserve">상급</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>알파 초안</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>변경 내역</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnemyGroupName</t>
-  </si>
-  <si>
-    <t>MinLevel</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxLevel</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>유닛 종류</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>유닛 그룹명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>최소 레벨</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 레벨</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>체력 성장치</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격력 성장치</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>방어력 성장치</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 코어</t>
-  </si>
-  <si>
-    <t>광역 코어</t>
-  </si>
-  <si>
-    <t>방어 코어</t>
-  </si>
-  <si>
-    <t>회복 코어</t>
-  </si>
-  <si>
-    <t>위압 코어</t>
-  </si>
-  <si>
-    <t>히어로젬의 힘을 가장 기본적인 형태로 다루는 코어. 안정적인 단일 공격을 사용할 수 있다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>히어로젬의 힘을 넓게 확산시키는 코어. 다수의 적을 동시에 공격할 수 있다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>히어로젬의 힘으로 보호막을 형성하는 코어. 적의 공격으로부터 아군을 지켜낸다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>히어로젬의 힘을 치유 에너지로 변환하는 코어. 부상당한 아군을 회복시킨다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>히어로젬의 힘으로 적의 전의를 꺾는 코어. 적 전체의 방어 능력을 약화시킨다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HC001</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HC002</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HC003</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HC004</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HC005</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HCS001</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HCS002</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HCS003</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HCS004</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HCS005</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>젬 파워</t>
-  </si>
-  <si>
-    <t>젬 익스플로전</t>
-  </si>
-  <si>
-    <t>젬 실드</t>
-  </si>
-  <si>
-    <t>젬 리커버리</t>
-  </si>
-  <si>
-    <t>젬 프레셔</t>
-  </si>
-  <si>
-    <t>히어로젬의 힘으로 적 1명에게 {WeaponSkillValue} 대미지를 준다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>히어로젬의 힘을 폭발시켜 모든 적에게 {WeaponSkillValue} 대미지를 준다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>히어로젬의 힘으로 보호막을 생성한다. 사용한 히어로가 다음 자신의 순서까지 받는 대미지가 {WeaponSkillValue} 감소한다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>히어로젬의 힘으로 아군 1명의 체력을 {WeaponSkillValue} 회복한다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>히어로젬의 힘으로 압박하여 모든 적의 방어력을 1턴 동안 {WeaponSkillValue} 감소시킨다.</t>
+    <t xml:space="preserve">알파 초안</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">변경 내역</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EnemyGroupName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MinLevel</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxLevel</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">유닛 종류</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">유닛 그룹명</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">최소 레벨</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">최대 레벨</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 성장치</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 성장치</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">방어력 성장치</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">기본 코어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">광역 코어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">방어 코어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회복 코어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">위압 코어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">히어로젬의 힘을 가장 기본적인 형태로 다루는 코어. 안정적인 단일 공격을 사용할 수 있다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">히어로젬의 힘을 넓게 확산시키는 코어. 다수의 적을 동시에 공격할 수 있다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">히어로젬의 힘으로 보호막을 형성하는 코어. 적의 공격으로부터 아군을 지켜낸다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">히어로젬의 힘을 치유 에너지로 변환하는 코어. 부상당한 아군을 회복시킨다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">히어로젬의 힘으로 적의 전의를 꺾는 코어. 적 전체의 방어 능력을 약화시킨다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HC001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HC002</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HC003</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HC004</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HC005</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HCS001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HCS002</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HCS003</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HCS004</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HCS005</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">젬 파워</t>
+  </si>
+  <si>
+    <t xml:space="preserve">젬 익스플로전</t>
+  </si>
+  <si>
+    <t xml:space="preserve">젬 실드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">젬 리커버리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">젬 프레셔</t>
+  </si>
+  <si>
+    <t xml:space="preserve">히어로젬의 힘으로 적 1명에게 {WeaponSkillValue} 대미지를 준다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">히어로젬의 힘을 폭발시켜 모든 적에게 {WeaponSkillValue} 대미지를 준다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">히어로젬의 힘으로 보호막을 생성한다. 사용한 히어로가 다음 자신의 순서까지 받는 대미지가 {WeaponSkillValue} 감소한다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">히어로젬의 힘으로 아군 1명의 체력을 {WeaponSkillValue} 회복한다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">히어로젬의 힘으로 압박하여 모든 적의 방어력을 1턴 동안 {WeaponSkillValue} 감소시킨다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1428,7 +1422,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>3 버프 4 디버프</t>
+      <t xml:space="preserve">3 버프 4 디버프</t>
     </r>
     <r>
       <rPr>
@@ -1438,608 +1432,608 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>)</t>
+      <t xml:space="preserve">)</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>저스티스</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS1010</t>
-  </si>
-  <si>
-    <t>HS1010</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS1020</t>
-  </si>
-  <si>
-    <t>HS1020</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS1030</t>
-  </si>
-  <si>
-    <t>HS1040</t>
-  </si>
-  <si>
-    <t>HS1011</t>
-  </si>
-  <si>
-    <t>HS1011</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS1021</t>
-  </si>
-  <si>
-    <t>HS1021</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS1031</t>
-  </si>
-  <si>
-    <t>HS1031</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS1041</t>
-  </si>
-  <si>
-    <t>HS1041</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>저스티스 등장!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>저스티스 등장!+</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>저스티스 펀치</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>저스티스 펀치+</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>저스티스 대쉬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>저스티스 대쉬+</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>저스티스 크래쉬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>저스티스 크래쉬+</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ReplaceSkillIndex</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>R0101</t>
+    <t xml:space="preserve">저스티스</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS1010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS1010</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS1020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS1020</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS1030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS1040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS1011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS1011</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS1021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS1021</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS1031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS1031</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS1041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS1041</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">저스티스 등장!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">저스티스 등장!+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">저스티스 펀치</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">저스티스 펀치+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">저스티스 대쉬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">저스티스 대쉬+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">저스티스 크래쉬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">저스티스 크래쉬+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ReplaceSkillIndex</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">R0101</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>R0102</t>
+    <t xml:space="preserve">R0102</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>R0103</t>
+    <t xml:space="preserve">R0103</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>R0101</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>R0102</t>
-  </si>
-  <si>
-    <t>R0103</t>
-  </si>
-  <si>
-    <t>R0102</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillRiskIndex</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>빈틈</t>
+    <t xml:space="preserve">R0101</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">R0102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R0103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R0102</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SkillRiskIndex</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">빈틈</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>자신 방어력 10% 감소</t>
+    <t xml:space="preserve">자신 방어력 10% 감소</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>힘 조절 실패</t>
+    <t xml:space="preserve">힘 조절 실패</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>이번 턴 {ClassSkillValue} 10% 감소
+    <t xml:space="preserve">이번 턴 {ClassSkillValue} 10% 감소
 예시) 100% → 90%</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>무리한 근성</t>
+    <t xml:space="preserve">무리한 근성</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>입힌 대미지의 10% 반동 피해</t>
+    <t xml:space="preserve">입힌 대미지의 10% 반동 피해</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>R0201</t>
+    <t xml:space="preserve">R0201</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>급발진</t>
+    <t xml:space="preserve">급발진</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>대상이 2명 이상일 경우, 무작위 대상 1명에게 피해 미적용</t>
+    <t xml:space="preserve">대상이 2명 이상일 경우, 무작위 대상 1명에게 피해 미적용</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>R0202</t>
+    <t xml:space="preserve">R0202</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>자의식 과잉</t>
+    <t xml:space="preserve">자의식 과잉</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>자신을 제외한 무작위 아군 1명에게 {ClassSkillValue}의 50% 대미지</t>
+    <t xml:space="preserve">자신을 제외한 무작위 아군 1명에게 {ClassSkillValue}의 50% 대미지</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>R0203</t>
+    <t xml:space="preserve">R0203</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>멘탈 붕괴</t>
+    <t xml:space="preserve">멘탈 붕괴</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>R0301</t>
+    <t xml:space="preserve">R0301</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>오발</t>
+    <t xml:space="preserve">오발</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>공격 대상이 다른 랜덤 적군 한 명 변경</t>
+    <t xml:space="preserve">공격 대상이 다른 랜덤 적군 한 명 변경</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>R0302</t>
+    <t xml:space="preserve">R0302</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>과열</t>
+    <t xml:space="preserve">과열</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>R0303</t>
+    <t xml:space="preserve">R0303</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>태만</t>
+    <t xml:space="preserve">태만</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>자신이 받는 대미지 10% 증가</t>
+    <t xml:space="preserve">자신이 받는 대미지 10% 증가</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>서브 효과가 있는 경우, {ClassSkillSubValue} = 0</t>
+    <t xml:space="preserve">서브 효과가 있는 경우, {ClassSkillSubValue} = 0</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>이번 턴 {ClassSkillValue} 10% 감소, 예시) 100% → 90%</t>
+    <t xml:space="preserve">이번 턴 {ClassSkillValue} 10% 감소, 예시) 100% → 90%</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>R0401</t>
+    <t xml:space="preserve">R0401</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>과한 헌신</t>
+    <t xml:space="preserve">과한 헌신</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>R0402</t>
+    <t xml:space="preserve">R0402</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>무리한 기도</t>
+    <t xml:space="preserve">무리한 기도</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>R0403</t>
-  </si>
-  <si>
-    <t>고양이 손</t>
+    <t xml:space="preserve">R0403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고양이 손</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>공격 스킬 사용 시, 적에게 입히는 대미지가 회복으로 전환</t>
+    <t xml:space="preserve">공격 스킬 사용 시, 적에게 입히는 대미지가 회복으로 전환</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>자신 현재 체력 최대 체력의 10% 감소 (단, 해당 효과로 인한 최소 HP = 1)</t>
+    <t xml:space="preserve">자신 현재 체력 최대 체력의 10% 감소 (단, 해당 효과로 인한 최소 HP = 1)</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>적 1명에게 {ClassSkillValue} 대미지를 입힌다. 대상이 전열일 경우 {ClassSkillValue}+{ClassSkillSubValue} 대미지를 입힌다. (적 전열이 있을 경우, 전열 우선 공격)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적 전열과 후열의 모든 적에게 {ClassSkillValue} 대미지를 준다. 1턴 동안 모든 적이 단일 공격 시 자신을 공격하게 한다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS2010</t>
-  </si>
-  <si>
-    <t>HS2010</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS2020</t>
-  </si>
-  <si>
-    <t>HS2020</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS2030</t>
-  </si>
-  <si>
-    <t>HS2030</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS2040</t>
-  </si>
-  <si>
-    <t>HS2040</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS2011</t>
-  </si>
-  <si>
-    <t>HS2011</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS2021</t>
-  </si>
-  <si>
-    <t>HS2021</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS2031</t>
-  </si>
-  <si>
-    <t>HS2031</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS2041</t>
-  </si>
-  <si>
-    <t>HS2041</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>루미나</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>플레어 봄</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>플레어 봄+</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>체인 라이팅</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>체인 라이팅+</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>솔라 프리즘</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>솔라 프리즘+</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>프리즘 익스플로전</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>프리즘 익스플로전+</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>전열의 적 한 명에게 {ClassSkillValue} 대미지를 입히고, 인접한 적 한 명에게 추가로 {ClassSkillSubValue} 대미지를 입힌다.</t>
-  </si>
-  <si>
-    <t>적 한 열에 {ClassSkillValue} 대미지를 입힌다.</t>
-  </si>
-  <si>
-    <t>적 전열과 후열의 모든 적에게 {ClassSkillValue} 대미지를 입힌다. 대상의 현재 체력이 50% 미만일 경우 {SubClassSkillSubValue} 대미지를 추가로 입힌다.</t>
-  </si>
-  <si>
-    <t>R0202</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>R0203</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>R0201</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS3010</t>
-  </si>
-  <si>
-    <t>HS3010</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS3020</t>
-  </si>
-  <si>
-    <t>HS3020</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS3030</t>
-  </si>
-  <si>
-    <t>HS3030</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS3040</t>
-  </si>
-  <si>
-    <t>HS3040</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS3011</t>
-  </si>
-  <si>
-    <t>HS3011</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS3021</t>
-  </si>
-  <si>
-    <t>HS3021</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS3031</t>
-  </si>
-  <si>
-    <t>HS3031</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS3041</t>
-  </si>
-  <si>
-    <t>HS3041</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>블랙 불릿</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>R0303</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>R0301</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>R0302</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>블랙 데빌 퍼펙트 에임 샷</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>프론트 라인 브레이크 불릿</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>트윈 트리거 더블 버스트</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>데드엔드 라스트 트리거</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>블랙 데빌 퍼펙트 에임 샷+</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>프론트 라인 브레이크 불릿+</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>트윈 트리거 더블 버스트+</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>데드엔드 라스트 트리거+</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적 1명에게 {ClassSkillValue} 대미지를 입힌다. 전열의 적을 공격 시, {ClassSkillValue}+{ClassSkillSubValue}대미지로 계산한다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적의 체력이 낮을 수록 높은 대미지를 입힌다. (기본 100% + 적의 최대 체력 대비 현재 체력 10%가 낮아질 때마다 {ClassSkillSubValue} 추가)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS4010</t>
-  </si>
-  <si>
-    <t>HS4010</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS4020</t>
-  </si>
-  <si>
-    <t>HS4020</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS4030</t>
-  </si>
-  <si>
-    <t>HS4030</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS4040</t>
-  </si>
-  <si>
-    <t>HS4040</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS4011</t>
-  </si>
-  <si>
-    <t>HS4011</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS4021</t>
-  </si>
-  <si>
-    <t>HS4021</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS4031</t>
-  </si>
-  <si>
-    <t>HS4031</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS4041</t>
-  </si>
-  <si>
-    <t>HS4041</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>R0401</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>R0403</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>R0402</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>네코밍</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>아픈 거 다 날아가라</t>
-  </si>
-  <si>
-    <t>널 위해 준비했어</t>
-  </si>
-  <si>
-    <t>우리 다 같이 힘내자</t>
-  </si>
-  <si>
-    <t>쓰러지면 안 돼</t>
-  </si>
-  <si>
-    <t>아픈 거 다 날아가라+</t>
-  </si>
-  <si>
-    <t>널 위해 준비했어+</t>
-  </si>
-  <si>
-    <t>우리 다 같이 힘내자+</t>
-  </si>
-  <si>
-    <t>쓰러지면 안 돼+</t>
-  </si>
-  <si>
-    <t>아군 1명 체력을 네코밍 최대 체력의 {ClassSkillValue} 회복</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적 1명에게 {ClassSkillValue}대미지를 입힌다. 입힌 대미지 만큼 랜덤 아군 1명의 체력을 회복한다</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>아군 1명의 체력을 네코밍 최대 체력의 {ClassSkillValue} 회복하고, 인접한 아군 1명의 체력을 자신 최대 체력의 {ClassSkillSubValue} 추가 회복한다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>리타이어한 아군 1명을 해당 아군 최대 체력의 {ClassSkillSubValue}로 부활시킨 후, 적 전체에 {ClassSkillValue} 대미지를 입힌다.
+    <t xml:space="preserve">적 1명에게 {ClassSkillValue} 대미지를 입힌다. 대상이 전열일 경우 {ClassSkillValue}+{ClassSkillSubValue} 대미지를 입힌다. (적 전열이 있을 경우, 전열 우선 공격)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적 전열과 후열의 모든 적에게 {ClassSkillValue} 대미지를 준다. 1턴 동안 모든 적이 단일 공격 시 자신을 공격하게 한다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS2010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS2010</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS2020</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS2030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS2030</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS2040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS2040</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS2011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS2011</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS2021</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS2031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS2031</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS2041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS2041</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">루미나</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">플레어 봄</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">플레어 봄+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">체인 라이팅</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">체인 라이팅+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">솔라 프리즘</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">솔라 프리즘+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">프리즘 익스플로전</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">프리즘 익스플로전+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">전열의 적 한 명에게 {ClassSkillValue} 대미지를 입히고, 인접한 적 한 명에게 추가로 {ClassSkillSubValue} 대미지를 입힌다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 한 열에 {ClassSkillValue} 대미지를 입힌다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 전열과 후열의 모든 적에게 {ClassSkillValue} 대미지를 입힌다. 대상의 현재 체력이 50% 미만일 경우 {SubClassSkillSubValue} 대미지를 추가로 입힌다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R0202</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">R0203</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">R0201</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS3010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS3010</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS3020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS3020</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS3030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS3030</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS3040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS3040</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS3011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS3011</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS3021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS3021</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS3031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS3031</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS3041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS3041</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">블랙 불릿</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">R0303</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">R0301</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">R0302</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">블랙 데빌 퍼펙트 에임 샷</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">프론트 라인 브레이크 불릿</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">트윈 트리거 더블 버스트</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">데드엔드 라스트 트리거</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">블랙 데빌 퍼펙트 에임 샷+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">프론트 라인 브레이크 불릿+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">트윈 트리거 더블 버스트+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">데드엔드 라스트 트리거+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적 1명에게 {ClassSkillValue} 대미지를 입힌다. 전열의 적을 공격 시, {ClassSkillValue}+{ClassSkillSubValue}대미지로 계산한다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적의 체력이 낮을 수록 높은 대미지를 입힌다. (기본 100% + 적의 최대 체력 대비 현재 체력 10%가 낮아질 때마다 {ClassSkillSubValue} 추가)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS4010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS4010</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS4020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS4020</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS4030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS4030</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS4040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS4040</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS4011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS4011</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS4021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS4021</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS4031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS4031</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HS4041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS4041</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">R0401</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">R0403</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">R0402</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">네코밍</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">아픈 거 다 날아가라</t>
+  </si>
+  <si>
+    <t xml:space="preserve">널 위해 준비했어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">우리 다 같이 힘내자</t>
+  </si>
+  <si>
+    <t xml:space="preserve">쓰러지면 안 돼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아픈 거 다 날아가라+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">널 위해 준비했어+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">우리 다 같이 힘내자+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">쓰러지면 안 돼+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아군 1명 체력을 네코밍 최대 체력의 {ClassSkillValue} 회복</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적 1명에게 {ClassSkillValue}대미지를 입힌다. 입힌 대미지 만큼 랜덤 아군 1명의 체력을 회복한다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">아군 1명의 체력을 네코밍 최대 체력의 {ClassSkillValue} 회복하고, 인접한 아군 1명의 체력을 자신 최대 체력의 {ClassSkillSubValue} 추가 회복한다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">리타이어한 아군 1명을 해당 아군 최대 체력의 {ClassSkillSubValue}로 부활시킨 후, 적 전체에 {ClassSkillValue} 대미지를 입힌다.
 단, 부활 효과는 전투당 1회만 적용되며, 이후 사용 시에는 적 전체 대미지만 적용된다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>{1,3,5,7}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>콘텐츠 확정 및 추가 필요 열 기입
+    <t xml:space="preserve">{1,3,5,7}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">콘텐츠 확정 및 추가 필요 열 기입
 1) EnemyUnit (필드 빌런)
  (1) 필드 빌런 종류 5종
    - maestrobot (마에스트로봇) / rifleman (빌런연합 소총수) / shielder (빌런연합 방패병) / tower (무인 중포탑) / monster (괴수, 콘셉트 변경 예정)
@@ -2058,162 +2052,162 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>마에스트로봇</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>FV20001</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>FV20002</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>FV20003</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>FV20004</t>
-  </si>
-  <si>
-    <t>FV20005</t>
-  </si>
-  <si>
-    <t>빌런연합 소총수</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>빌런연합 방패병</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무인 중포탑</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>괴수</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>프로파간다용 드론</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>가장 흔한 원거리 병졸</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>아군 보호형 탱커</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>고정형 한방 딜러</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대형 체급 압박형 빌런</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>경험치 성장치</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LevelGrowthExperiencePoint</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LevelGrowthMaxHP</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LevelGrowthAtk</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LevelGrowthDef</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>원거리 사격</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대신 맞기</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>충전 포격</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>발톱 후리기</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>박치기</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>타깃 지정</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>자폭</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>방패 치기</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>가장 가까운 히어로 1명을 표적으로 지정</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적군 스킬 1 효과
+    <t xml:space="preserve">마에스트로봇</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">FV20001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">FV20002</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">FV20003</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">FV20004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FV20005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">빌런연합 소총수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">빌런연합 방패병</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무인 중포탑</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">괴수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">프로파간다용 드론</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">가장 흔한 원거리 병졸</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">아군 보호형 탱커</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">고정형 한방 딜러</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">대형 체급 압박형 빌런</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">경험치 성장치</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LevelGrowthExperiencePoint</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LevelGrowthMaxHP</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LevelGrowthAtk</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LevelGrowthDef</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">원거리 사격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">대신 맞기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">충전 포격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">발톱 후리기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">박치기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">타깃 지정</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">자폭</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">방패 치기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">가장 가까운 히어로 1명을 표적으로 지정</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적군 스킬 1 효과
 (0 공격 1 회복 2 부활 3 버프 4 디버프)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>{1, 3, 5, 7}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnemySkill2SubValue</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnemySkill1SubValue</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>타깃 유닛을 향해 전진 후 자폭
+    <t xml:space="preserve">{1, 3, 5, 7}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EnemySkill2SubValue</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EnemySkill1SubValue</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">타깃 유닛을 향해 전진 후 자폭
 타깃 유닛에게 {EnemySkill2Value}
 타깃 인접 유닛에게 {EnemySkill2SubValue}를 준 뒤 자신의 체력 0 처리</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>상대 전열 또는 후열 단일 유닛에게 {EnemySkill1Value} 만큼 대미지</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>상대 전열 우선 단일 유닛에게 {EnemySkill1Value} 만큼 대미지</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>다음 자신의 차례까지 아군 유닛을 공격하는 플레이어의 단일 공격을 1회 막기 (대상 위치로 이동해 피해를 대신 받고 원래 위치로 복귀)
+    <t xml:space="preserve">상대 전열 또는 후열 단일 유닛에게 {EnemySkill1Value} 만큼 대미지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">상대 전열 우선 단일 유닛에게 {EnemySkill1Value} 만큼 대미지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">다음 자신의 차례까지 아군 유닛을 공격하는 플레이어의 단일 공격을 1회 막기 (대상 위치로 이동해 피해를 대신 받고 원래 위치로 복귀)
 (단, 자신을 공격하는 단일 공격이나 광역 피해는 막기 대상으로 취급하지 않음)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>(1턴) 가장 가까운 히어로 1명을 표적으로 지정 (가장 가까운 유닛이 둘 이상일 경우 대상은 랜덤)
+    <t xml:space="preserve">(1턴) 가장 가까운 히어로 1명을 표적으로 지정 (가장 가까운 유닛이 둘 이상일 경우 대상은 랜덤)
 (2턴) 해당 유닛에게 '자폭' 실행 - 대미지 계산 후 마에스트로봇 전장 제거</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>(매 턴) '원거리 사격' 실행
+    <t xml:space="preserve">(매 턴) '원거리 사격' 실행
 우선 순위
 1. 같은 행에 있는 히어로를 우선 표적으로 삼는다.
 2. 같은 행 표적이 여럿이면 현재 체력이 낮은 히어로를 선택한다.
@@ -2221,92 +2215,98 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>(매 턴) 
+    <t xml:space="preserve">(매 턴) 
 - 아군 유닛 중, 체력 30% 미만 유닛이 1명 이상 있는 경우, '대신 맞기' 실행
 - 아닌 경우 가장 가까운 유닛에게 '방패 치기' 실행</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>(매 턴) 랜덤 히어로 1명을 대상으로 '충전 포격' 실행</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>히어로 유닛 1체에 {EnemySkill2Value} 만큼 대미지를 주고, 해당 행에 후열에 있는 히어로에게 {EnemySkill2SubValue}를 준다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{7}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(매 턴)
+    <t xml:space="preserve">(매 턴) 랜덤 히어로 1명을 대상으로 '충전 포격' 실행</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">히어로 유닛 1체에 {EnemySkill2Value} 만큼 대미지를 주고, 해당 행에 후열에 있는 히어로에게 {EnemySkill2SubValue}를 준다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">{7}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(매 턴)
 - 같은 행에 히어로가 없는 경우, '발톱 후리기' 실행
 - 같은 행에 히어로가 1명 있는 경우, '발톱 후리기' 실행
 - 같은 행에 히어로가 2명 있는 경우, '박치기' 실행</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>(1턴) 히어로 1명 또는 해당 타일을 지정하고 피해 범위 표시
+    <t xml:space="preserve">(1턴) 히어로 1명 또는 해당 타일을 지정하고 피해 범위 표시
 (2턴) 해당 유닛에게 {EnemySkill1Value} 만큼 대미지
 (2턴이 오기 전, 무인 중포탑이 대미지를 받을 시, 스킬 취소 → 2턴째 다시 충전 시작)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Character3StudySkill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Character4StudySkill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Character1StudySkill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Character2StudySkill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐릭터1 (저스티스)
+    <t xml:space="preserve">Character3StudySkill</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Character4StudySkill</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Character1StudySkill</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Character2StudySkill</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">캐릭터1 (저스티스)
 배우는 스킬</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>캐릭터2 (루미나)
+    <t xml:space="preserve">캐릭터2 (루미나)
 배우는 스킬</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>캐릭터3 (블랙 불릿)
+    <t xml:space="preserve">캐릭터3 (블랙 불릿)
 배우는 스킬</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>캐릭터4 (네코밍)
+    <t xml:space="preserve">캐릭터4 (네코밍)
 배우는 스킬</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>{HS1010,HS1020,HS1030,HS1040,HS1011,HS1021,HS1031,HS1041}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{HS2020,HS2020,HS2030,HS2040,HS2011,HS2021,HS2031,HS2041}</t>
-  </si>
-  <si>
-    <t>{HS3030,HS3020,HS3030,HS3040,HS3011,HS3021,HS3031,HS3041}</t>
-  </si>
-  <si>
-    <t>{HS4040,HS4020,HS4030,HS4040,HS4011,HS4021,HS4031,HS4041}</t>
-  </si>
-  <si>
-    <t>{HC001,HC002,HC003,HC004,HC005}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>list&lt;string&gt;</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t xml:space="preserve">{HS1010,HS1020,HS1030,HS1040,HS1011,HS1021,HS1031,HS1041}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">{HS2020,HS2020,HS2030,HS2040,HS2011,HS2021,HS2031,HS2041}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{HS3030,HS3020,HS3030,HS3040,HS3011,HS3021,HS3031,HS3041}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{HS4040,HS4020,HS4030,HS4040,HS4011,HS4021,HS4031,HS4041}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{HC001,HC002,HC003,HC004,HC005}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">list&lt;string&gt;</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">{HS2010,HS2020,HS2030,HS2040,HS2011,HS2021,HS2031,HS2041}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{HS4010,HS4020,HS4030,HS4040,HS4011,HS4021,HS4031,HS4041}</t>
   </si>
 </sst>
 </file>
@@ -2709,7 +2709,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -2720,7 +2720,7 @@
           </a:r>
           <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -2773,7 +2773,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -2784,7 +2784,7 @@
           </a:r>
           <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -2837,7 +2837,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -2848,7 +2848,7 @@
           </a:r>
           <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -2901,7 +2901,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -2912,7 +2912,7 @@
           </a:r>
           <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -2965,7 +2965,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -2984,7 +2984,7 @@
           </a:r>
           <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -3202,6 +3202,7 @@
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:custDash/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
@@ -3209,6 +3210,7 @@
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:custDash/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
@@ -3216,6 +3218,7 @@
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:custDash/>
           <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
@@ -3324,7 +3327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0AF93A4-1273-423C-B589-7C2465F14193}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
@@ -3338,7 +3341,6 @@
     <col min="16" max="16" width="24.58203125" style="11" customWidth="1"/>
     <col min="17" max="17" width="24.33203125" style="11" customWidth="1"/>
     <col min="18" max="62" width="15.58203125" style="11" customWidth="1"/>
-    <col min="63" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -3560,7 +3562,7 @@
         <v>3</v>
       </c>
       <c r="M7" s="44" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="N7" s="34" t="s">
         <v>547</v>
@@ -3662,7 +3664,7 @@
         <v>2</v>
       </c>
       <c r="M9" s="44" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="N9" s="34" t="s">
         <v>547</v>
